--- a/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
+++ b/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402A7A37-6312-4940-AC12-80A70AB1FAEF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A13C3D-8913-474B-976B-A020648C38F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="9" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="1" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="109">
   <si>
     <t>страна</t>
   </si>
@@ -352,14 +352,30 @@
   </si>
   <si>
     <t>Population (thousands, on January 1st)</t>
+  </si>
+  <si>
+    <t>Уругвай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana M. Rothman, "Evolution of Fertility in Argentina and Uruguay", International Population Conference. London. 1969, vol. I, </t>
+  </si>
+  <si>
+    <t>тж. Finch, "A Political Economy of Uruguay since 1870", University of Liverpool, 1871, стр. 24.</t>
+  </si>
+  <si>
+    <t>(International Union for the Scientific Study of the Population, Liege, 1971) vol. 1, стр. 716</t>
+  </si>
+  <si>
+    <t>Для Уругвая (1895-1949):</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -384,7 +400,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,6 +410,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -424,6 +446,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,129 +764,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C2E48C-64F2-4716-9126-743AC29B124D}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1571,7 +1617,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C0617D-C32F-4BD6-B0C3-D321B90C0E61}">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" customWidth="1"/>
@@ -2066,79 +2112,79 @@
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="11">
         <v>46.15</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="11">
         <v>45.9</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="11">
         <v>45.65</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="11">
         <v>45.4</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="11">
         <v>45.15</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="11">
         <v>44.96</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="11">
         <v>44.86</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="11">
         <v>44.746666666666663</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="11">
         <v>44.613333333333337</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="11">
         <v>44.48</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="11">
         <v>44.160000000000004</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="14">
         <v>46.2</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="14">
         <v>45.07</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="14">
         <v>42.57</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="14">
         <v>37.58</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="14">
         <v>34.51</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="14">
         <v>33.14</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="14">
         <v>31.33</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="14">
         <v>27.4</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="14">
         <v>23.52</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="14">
         <v>21.51</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="14">
         <v>18.57</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="14">
         <v>16.29</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="14">
         <v>15</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="14">
         <v>14.1</v>
       </c>
     </row>
@@ -2931,12 +2977,179 @@
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="13">
+        <v>43.4</v>
+      </c>
+      <c r="C21" s="13">
+        <v>38.9</v>
+      </c>
+      <c r="D21" s="13">
+        <v>37.6</v>
+      </c>
+      <c r="E21" s="13">
+        <v>36.5</v>
+      </c>
+      <c r="F21" s="13">
+        <v>31.9</v>
+      </c>
+      <c r="G21" s="13">
+        <v>30.1</v>
+      </c>
+      <c r="H21" s="13">
+        <v>28.6</v>
+      </c>
+      <c r="I21" s="13">
+        <v>25.8</v>
+      </c>
+      <c r="J21" s="13">
+        <v>22.3</v>
+      </c>
+      <c r="K21" s="13">
+        <v>21.6</v>
+      </c>
+      <c r="L21" s="13">
+        <v>21.1</v>
+      </c>
+      <c r="M21" s="3">
+        <v>21.28</v>
+      </c>
+      <c r="N21" s="3">
+        <v>21.8</v>
+      </c>
+      <c r="O21" s="3">
+        <v>21.75</v>
+      </c>
+      <c r="P21" s="3">
+        <v>20.57</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>20.32</v>
+      </c>
+      <c r="R21" s="3">
+        <v>20.6</v>
+      </c>
+      <c r="S21" s="3">
+        <v>18.07</v>
+      </c>
+      <c r="T21" s="3">
+        <v>17.93</v>
+      </c>
+      <c r="U21" s="3">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="V21" s="3">
+        <v>16.98</v>
+      </c>
+      <c r="W21" s="3">
+        <v>15.53</v>
+      </c>
+      <c r="X21" s="3">
+        <v>14.66</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>14.22</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>12.66</v>
+      </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B26" s="12"/>
+      <c r="D26" s="3"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B27" s="12"/>
+      <c r="D27" s="3"/>
+      <c r="M27" s="12"/>
+      <c r="O27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="M28" s="12"/>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="M29" s="12"/>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="M31" s="12"/>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="M32" s="12"/>
+      <c r="O32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+    </row>
+    <row r="33" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M33" s="12"/>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M34" s="12"/>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M35" s="12"/>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="36" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M36" s="12"/>
+      <c r="O36" s="3"/>
+    </row>
+    <row r="37" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M37" s="12"/>
+      <c r="O37" s="3"/>
+    </row>
+    <row r="38" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M38" s="12"/>
+      <c r="O38" s="3"/>
+    </row>
+    <row r="39" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M39" s="12"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M40" s="12"/>
+      <c r="O40" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2946,7 +3159,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40E0A31-8EE1-4474-96EA-571AB8EBD4C3}">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
@@ -3441,79 +3654,79 @@
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="11">
         <v>28.520000000000003</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="11">
         <v>27.640000000000004</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="11">
         <v>27.240000000000002</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="11">
         <v>26.879999999999995</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="11">
         <v>26.580000000000002</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="11">
         <v>26.32</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="11">
         <v>26.119999999999997</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="11">
         <v>25.32</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="11">
         <v>23.62</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="11">
         <v>21.919999999999998</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="11">
         <v>19.559999999999999</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="14">
         <v>16.309999999999999</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="14">
         <v>14.6</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="14">
         <v>12.95</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="14">
         <v>11.32</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="14">
         <v>10.050000000000001</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="14">
         <v>9.1199999999999992</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="14">
         <v>8.23</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="14">
         <v>7.37</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="14">
         <v>6.8</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="14">
         <v>6.41</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="14">
         <v>6.11</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="14">
         <v>5.82</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="14">
         <v>5.89</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="14">
         <v>6.26</v>
       </c>
     </row>
@@ -4302,10 +4515,90 @@
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="C21" s="11">
+        <v>13.7</v>
+      </c>
+      <c r="D21" s="11">
+        <v>14</v>
+      </c>
+      <c r="E21" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="F21" s="11">
+        <v>14.1</v>
+      </c>
+      <c r="G21" s="11">
+        <v>12.6</v>
+      </c>
+      <c r="H21" s="11">
+        <v>11.9</v>
+      </c>
+      <c r="I21" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="J21" s="11">
+        <v>11.1</v>
+      </c>
+      <c r="K21" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="L21" s="11">
+        <v>9.1</v>
+      </c>
+      <c r="M21" s="3">
+        <v>10.53</v>
+      </c>
+      <c r="N21" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="O21" s="3">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="P21" s="3">
+        <v>9.68</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="R21" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="S21" s="3">
+        <v>9.77</v>
+      </c>
+      <c r="T21" s="3">
+        <v>9.84</v>
+      </c>
+      <c r="U21" s="3">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="V21" s="3">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="W21" s="3">
+        <v>9.51</v>
+      </c>
+      <c r="X21" s="3">
+        <v>9.33</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>9.57</v>
+      </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
     </row>

--- a/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
+++ b/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A13C3D-8913-474B-976B-A020648C38F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C358C0-E810-49C1-932C-4B0FD7BB8FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="1" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
+    <workbookView xWindow="19095" yWindow="540" windowWidth="18960" windowHeight="23040" activeTab="2" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="115">
   <si>
     <t>страна</t>
   </si>
@@ -367,6 +367,24 @@
   </si>
   <si>
     <t>Для Уругвая (1895-1949):</t>
+  </si>
+  <si>
+    <t>Аргентина-Ротман</t>
+  </si>
+  <si>
+    <t>Для Аргентины (1895-1949, вариант Ротман):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rothman, "Evolution of Fertility in Argentina and Uruguay", стр. 716 </t>
+  </si>
+  <si>
+    <t>1880-84</t>
+  </si>
+  <si>
+    <t>1885-89</t>
+  </si>
+  <si>
+    <t>1890-94</t>
   </si>
 </sst>
 </file>
@@ -432,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -450,6 +468,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -764,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C2E48C-64F2-4716-9126-743AC29B124D}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -818,53 +838,39 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
@@ -907,6 +913,30 @@
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1617,14 +1647,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C0617D-C32F-4BD6-B0C3-D321B90C0E61}">
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="29" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -1639,562 +1669,592 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="O3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="W3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="X3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="Y3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="AB3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="AC3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="6">
         <v>43.1</v>
       </c>
-      <c r="C4" s="6">
+      <c r="F4" s="6">
         <v>41.8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="G4" s="6">
         <v>43.6</v>
       </c>
-      <c r="E4" s="6">
+      <c r="H4" s="6">
         <v>44.5</v>
       </c>
-      <c r="F4" s="6">
+      <c r="I4" s="6">
         <v>41.4</v>
       </c>
-      <c r="G4" s="6">
+      <c r="J4" s="6">
         <v>41.2</v>
       </c>
-      <c r="H4" s="6">
+      <c r="K4" s="6">
         <v>43.1</v>
       </c>
-      <c r="I4" s="6">
+      <c r="L4" s="6">
         <v>39.9</v>
       </c>
-      <c r="J4" s="6">
+      <c r="M4" s="6">
         <v>40.200000000000003</v>
       </c>
-      <c r="K4" s="6">
+      <c r="N4" s="6">
         <v>41.5</v>
       </c>
-      <c r="L4" s="6">
+      <c r="O4" s="6">
         <v>43.6</v>
       </c>
-      <c r="M4" s="3">
+      <c r="P4" s="3">
         <v>47.31</v>
       </c>
-      <c r="N4" s="3">
+      <c r="Q4" s="3">
         <v>46.86</v>
       </c>
-      <c r="O4" s="3">
+      <c r="R4" s="3">
         <v>43.45</v>
       </c>
-      <c r="P4" s="3">
+      <c r="S4" s="3">
         <v>39.74</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="T4" s="3">
         <v>36.270000000000003</v>
       </c>
-      <c r="R4" s="3">
+      <c r="U4" s="3">
         <v>34.44</v>
       </c>
-      <c r="S4" s="3">
+      <c r="V4" s="3">
         <v>32.340000000000003</v>
       </c>
-      <c r="T4" s="3">
+      <c r="W4" s="3">
         <v>30.44</v>
       </c>
-      <c r="U4" s="3">
+      <c r="X4" s="3">
         <v>27.7</v>
       </c>
-      <c r="V4" s="3">
+      <c r="Y4" s="3">
         <v>25.07</v>
       </c>
-      <c r="W4" s="3">
+      <c r="Z4" s="3">
         <v>23.18</v>
       </c>
-      <c r="X4" s="3">
+      <c r="AA4" s="3">
         <v>21.52</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="AB4" s="3">
         <v>19.79</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="AC4" s="3">
         <v>17.690000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="6">
         <v>46.7</v>
       </c>
-      <c r="C5" s="6">
+      <c r="F5" s="6">
         <v>46.9</v>
       </c>
-      <c r="D5" s="6">
+      <c r="G5" s="6">
         <v>48.2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="H5" s="6">
         <v>48.9</v>
       </c>
-      <c r="F5" s="6">
+      <c r="I5" s="6">
         <v>44.7</v>
       </c>
-      <c r="G5" s="6">
+      <c r="J5" s="6">
         <v>44.9</v>
       </c>
-      <c r="H5" s="6">
+      <c r="K5" s="6">
         <v>46.2</v>
       </c>
-      <c r="I5" s="6">
+      <c r="L5" s="6">
         <v>44.6</v>
       </c>
-      <c r="J5" s="6">
+      <c r="M5" s="6">
         <v>43.3</v>
       </c>
-      <c r="K5" s="6">
+      <c r="N5" s="6">
         <v>42.8</v>
       </c>
-      <c r="L5" s="6">
+      <c r="O5" s="6">
         <v>42.7</v>
       </c>
-      <c r="M5" s="3">
+      <c r="P5" s="3">
         <v>45.46</v>
       </c>
-      <c r="N5" s="3">
+      <c r="Q5" s="3">
         <v>45.87</v>
       </c>
-      <c r="O5" s="3">
+      <c r="R5" s="3">
         <v>43.65</v>
       </c>
-      <c r="P5" s="3">
+      <c r="S5" s="3">
         <v>36.68</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="T5" s="3">
         <v>30.97</v>
       </c>
-      <c r="R5" s="3">
+      <c r="U5" s="3">
         <v>30.09</v>
       </c>
-      <c r="S5" s="3">
+      <c r="V5" s="3">
         <v>30.46</v>
       </c>
-      <c r="T5" s="3">
+      <c r="W5" s="3">
         <v>29.03</v>
       </c>
-      <c r="U5" s="3">
+      <c r="X5" s="3">
         <v>25.05</v>
       </c>
-      <c r="V5" s="3">
+      <c r="Y5" s="3">
         <v>21.68</v>
       </c>
-      <c r="W5" s="3">
+      <c r="Z5" s="3">
         <v>18.510000000000002</v>
       </c>
-      <c r="X5" s="3">
+      <c r="AA5" s="3">
         <v>16.72</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="AB5" s="3">
         <v>15.25</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="AC5" s="3">
         <v>13.8</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6">
         <v>45.8</v>
       </c>
-      <c r="D6" s="6">
+      <c r="G6" s="6">
         <v>43.6</v>
       </c>
-      <c r="E6" s="6">
+      <c r="H6" s="6">
         <v>46.6</v>
       </c>
-      <c r="F6" s="6">
+      <c r="I6" s="6">
         <v>43.2</v>
       </c>
-      <c r="G6" s="6">
+      <c r="J6" s="6">
         <v>48.3</v>
       </c>
-      <c r="H6" s="6">
+      <c r="K6" s="6">
         <v>49.2</v>
       </c>
-      <c r="I6" s="6">
+      <c r="L6" s="6">
         <v>46.2</v>
       </c>
-      <c r="J6" s="6">
+      <c r="M6" s="6">
         <v>44.2</v>
       </c>
-      <c r="K6" s="6">
+      <c r="N6" s="6">
         <v>45.2</v>
       </c>
-      <c r="L6" s="6">
+      <c r="O6" s="6">
         <v>49.1</v>
       </c>
-      <c r="M6" s="3">
+      <c r="P6" s="3">
         <v>51.08</v>
       </c>
-      <c r="N6" s="3">
+      <c r="Q6" s="3">
         <v>50.11</v>
       </c>
-      <c r="O6" s="3">
+      <c r="R6" s="3">
         <v>47.47</v>
       </c>
-      <c r="P6" s="3">
+      <c r="S6" s="3">
         <v>45.65</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="T6" s="3">
         <v>44.47</v>
       </c>
-      <c r="R6" s="3">
+      <c r="U6" s="3">
         <v>43.87</v>
       </c>
-      <c r="S6" s="3">
+      <c r="V6" s="3">
         <v>42.97</v>
       </c>
-      <c r="T6" s="3">
+      <c r="W6" s="3">
         <v>40.74</v>
       </c>
-      <c r="U6" s="3">
+      <c r="X6" s="3">
         <v>38.950000000000003</v>
       </c>
-      <c r="V6" s="3">
+      <c r="Y6" s="3">
         <v>36.51</v>
       </c>
-      <c r="W6" s="3">
+      <c r="Z6" s="3">
         <v>33.270000000000003</v>
       </c>
-      <c r="X6" s="3">
+      <c r="AA6" s="3">
         <v>29.42</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="AB6" s="3">
         <v>27.15</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="AC6" s="3">
         <v>24.95</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
         <v>43</v>
       </c>
-      <c r="D7" s="6">
+      <c r="G7" s="6">
         <v>44</v>
       </c>
-      <c r="E7" s="6">
+      <c r="H7" s="6">
         <v>44.1</v>
       </c>
-      <c r="F7" s="6">
+      <c r="I7" s="6">
         <v>44.1</v>
       </c>
-      <c r="G7" s="6">
+      <c r="J7" s="6">
         <v>44.6</v>
       </c>
-      <c r="H7" s="6">
+      <c r="K7" s="6">
         <v>44.9</v>
       </c>
-      <c r="I7" s="6">
+      <c r="L7" s="6">
         <v>43.3</v>
       </c>
-      <c r="J7" s="6">
+      <c r="M7" s="6">
         <v>42.6</v>
       </c>
-      <c r="K7" s="6">
+      <c r="N7" s="6">
         <v>42.4</v>
       </c>
-      <c r="L7" s="6">
+      <c r="O7" s="6">
         <v>43.4</v>
       </c>
-      <c r="M7" s="3">
+      <c r="P7" s="3">
         <v>46.64</v>
       </c>
-      <c r="N7" s="3">
+      <c r="Q7" s="3">
         <v>46.59</v>
       </c>
-      <c r="O7" s="3">
+      <c r="R7" s="3">
         <v>44.78</v>
       </c>
-      <c r="P7" s="3">
+      <c r="S7" s="3">
         <v>40.090000000000003</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="T7" s="3">
         <v>34.619999999999997</v>
       </c>
-      <c r="R7" s="3">
+      <c r="U7" s="3">
         <v>32.04</v>
       </c>
-      <c r="S7" s="3">
+      <c r="V7" s="3">
         <v>30.25</v>
       </c>
-      <c r="T7" s="3">
+      <c r="W7" s="3">
         <v>27.58</v>
       </c>
-      <c r="U7" s="3">
+      <c r="X7" s="3">
         <v>26.55</v>
       </c>
-      <c r="V7" s="3">
+      <c r="Y7" s="3">
         <v>23.98</v>
       </c>
-      <c r="W7" s="3">
+      <c r="Z7" s="3">
         <v>21.31</v>
       </c>
-      <c r="X7" s="3">
+      <c r="AA7" s="3">
         <v>18.59</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="AB7" s="3">
         <v>16.03</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="AC7" s="3">
         <v>14.33</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="6">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6">
         <v>46.5</v>
-      </c>
-      <c r="G8" s="6">
-        <v>47.7</v>
-      </c>
-      <c r="H8" s="6">
-        <v>49.1</v>
-      </c>
-      <c r="I8" s="6">
-        <v>48.5</v>
       </c>
       <c r="J8" s="6">
         <v>47.7</v>
       </c>
       <c r="K8" s="6">
+        <v>49.1</v>
+      </c>
+      <c r="L8" s="6">
+        <v>48.5</v>
+      </c>
+      <c r="M8" s="6">
+        <v>47.7</v>
+      </c>
+      <c r="N8" s="6">
         <v>46</v>
       </c>
-      <c r="L8" s="6">
+      <c r="O8" s="6">
         <v>45.9</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>44.86</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>44.2</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>43.39</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>42.32</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>40.090000000000003</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>36.950000000000003</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>34.17</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>31.05</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>29.16</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>27.08</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>24.67</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AA8" s="3">
         <v>22.76</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>20.63</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>17.62</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="11">
         <v>46.15</v>
       </c>
-      <c r="C9" s="11">
+      <c r="F9" s="11">
         <v>45.9</v>
       </c>
-      <c r="D9" s="11">
+      <c r="G9" s="11">
         <v>45.65</v>
       </c>
-      <c r="E9" s="11">
+      <c r="H9" s="11">
         <v>45.4</v>
       </c>
-      <c r="F9" s="11">
+      <c r="I9" s="11">
         <v>45.15</v>
       </c>
-      <c r="G9" s="11">
+      <c r="J9" s="11">
         <v>44.96</v>
       </c>
-      <c r="H9" s="11">
+      <c r="K9" s="11">
         <v>44.86</v>
       </c>
-      <c r="I9" s="11">
+      <c r="L9" s="11">
         <v>44.746666666666663</v>
       </c>
-      <c r="J9" s="11">
+      <c r="M9" s="11">
         <v>44.613333333333337</v>
       </c>
-      <c r="K9" s="11">
+      <c r="N9" s="11">
         <v>44.48</v>
       </c>
-      <c r="L9" s="11">
+      <c r="O9" s="11">
         <v>44.160000000000004</v>
       </c>
-      <c r="M9" s="14">
+      <c r="P9" s="14">
         <v>46.2</v>
       </c>
-      <c r="N9" s="14">
+      <c r="Q9" s="14">
         <v>45.07</v>
       </c>
-      <c r="O9" s="14">
+      <c r="R9" s="14">
         <v>42.57</v>
       </c>
-      <c r="P9" s="14">
+      <c r="S9" s="14">
         <v>37.58</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="T9" s="14">
         <v>34.51</v>
       </c>
-      <c r="R9" s="14">
+      <c r="U9" s="14">
         <v>33.14</v>
       </c>
-      <c r="S9" s="14">
+      <c r="V9" s="14">
         <v>31.33</v>
       </c>
-      <c r="T9" s="14">
+      <c r="W9" s="14">
         <v>27.4</v>
       </c>
-      <c r="U9" s="14">
+      <c r="X9" s="14">
         <v>23.52</v>
       </c>
-      <c r="V9" s="14">
+      <c r="Y9" s="14">
         <v>21.51</v>
       </c>
-      <c r="W9" s="14">
+      <c r="Z9" s="14">
         <v>18.57</v>
       </c>
-      <c r="X9" s="14">
+      <c r="AA9" s="14">
         <v>16.29</v>
       </c>
-      <c r="Y9" s="14">
+      <c r="AB9" s="14">
         <v>15</v>
       </c>
-      <c r="Z9" s="14">
+      <c r="AC9" s="14">
         <v>14.1</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -2203,654 +2263,681 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
-      <c r="M10" s="3">
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="3">
         <v>44.07</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>42.93</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>42.14</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>39.26</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>35.950000000000003</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>35.08</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>36.81</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>36.07</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>33.15</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>29.52</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>25.29</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>23.19</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>22.54</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>22.11</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="6">
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6">
         <v>44.5</v>
       </c>
-      <c r="L11" s="6">
+      <c r="O11" s="6">
         <v>44.9</v>
       </c>
-      <c r="M11" s="3">
+      <c r="P11" s="3">
         <v>47.96</v>
       </c>
-      <c r="N11" s="3">
+      <c r="Q11" s="3">
         <v>47.52</v>
       </c>
-      <c r="O11" s="3">
+      <c r="R11" s="3">
         <v>46.17</v>
       </c>
-      <c r="P11" s="3">
+      <c r="S11" s="3">
         <v>43.92</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="T11" s="3">
         <v>41.24</v>
       </c>
-      <c r="R11" s="3">
+      <c r="U11" s="3">
         <v>38.299999999999997</v>
       </c>
-      <c r="S11" s="3">
+      <c r="V11" s="3">
         <v>35.46</v>
       </c>
-      <c r="T11" s="3">
+      <c r="W11" s="3">
         <v>32.96</v>
       </c>
-      <c r="U11" s="3">
+      <c r="X11" s="3">
         <v>29.58</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Y11" s="3">
         <v>25.67</v>
       </c>
-      <c r="W11" s="3">
+      <c r="Z11" s="3">
         <v>22.84</v>
       </c>
-      <c r="X11" s="3">
+      <c r="AA11" s="3">
         <v>21.34</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="AB11" s="3">
         <v>19.21</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="AC11" s="3">
         <v>17.309999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="6">
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6">
         <v>45.1</v>
       </c>
-      <c r="L12" s="6">
+      <c r="O12" s="6">
         <v>47</v>
       </c>
-      <c r="M12" s="3">
+      <c r="P12" s="3">
         <v>43.1</v>
       </c>
-      <c r="N12" s="3">
+      <c r="Q12" s="3">
         <v>43.66</v>
       </c>
-      <c r="O12" s="3">
+      <c r="R12" s="3">
         <v>43.83</v>
       </c>
-      <c r="P12" s="3">
+      <c r="S12" s="3">
         <v>43.34</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="T12" s="3">
         <v>42.04</v>
       </c>
-      <c r="R12" s="3">
+      <c r="U12" s="3">
         <v>40.76</v>
       </c>
-      <c r="S12" s="3">
+      <c r="V12" s="3">
         <v>38.880000000000003</v>
       </c>
-      <c r="T12" s="3">
+      <c r="W12" s="3">
         <v>37.08</v>
       </c>
-      <c r="U12" s="3">
+      <c r="X12" s="3">
         <v>34.81</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Y12" s="3">
         <v>31.6</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Z12" s="3">
         <v>28.66</v>
       </c>
-      <c r="X12" s="3">
+      <c r="AA12" s="3">
         <v>26.8</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AB12" s="3">
         <v>24.83</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AC12" s="3">
         <v>22.93</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6">
         <v>43.8</v>
       </c>
-      <c r="D13" s="6">
+      <c r="G13" s="6">
         <v>43.5</v>
       </c>
-      <c r="E13" s="6">
+      <c r="H13" s="6">
         <v>44.7</v>
       </c>
-      <c r="F13" s="6">
+      <c r="I13" s="6">
         <v>42.9</v>
       </c>
-      <c r="G13" s="6">
+      <c r="J13" s="6">
         <v>46.6</v>
       </c>
-      <c r="H13" s="6">
+      <c r="K13" s="6">
         <v>47.1</v>
       </c>
-      <c r="I13" s="6">
+      <c r="L13" s="6">
         <v>46.5</v>
       </c>
-      <c r="J13" s="6">
+      <c r="M13" s="6">
         <v>45.4</v>
       </c>
-      <c r="K13" s="6">
+      <c r="N13" s="6">
         <v>45.2</v>
       </c>
-      <c r="L13" s="6">
+      <c r="O13" s="6">
         <v>44.8</v>
       </c>
-      <c r="M13" s="3">
+      <c r="P13" s="3">
         <v>47.18</v>
       </c>
-      <c r="N13" s="3">
+      <c r="Q13" s="3">
         <v>47.39</v>
       </c>
-      <c r="O13" s="3">
+      <c r="R13" s="3">
         <v>46.99</v>
       </c>
-      <c r="P13" s="3">
+      <c r="S13" s="3">
         <v>44.96</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="T13" s="3">
         <v>42.46</v>
       </c>
-      <c r="R13" s="3">
+      <c r="U13" s="3">
         <v>40.79</v>
       </c>
-      <c r="S13" s="3">
+      <c r="V13" s="3">
         <v>38.47</v>
       </c>
-      <c r="T13" s="3">
+      <c r="W13" s="3">
         <v>35.07</v>
       </c>
-      <c r="U13" s="3">
+      <c r="X13" s="3">
         <v>32.270000000000003</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Y13" s="3">
         <v>29.67</v>
       </c>
-      <c r="W13" s="3">
+      <c r="Z13" s="3">
         <v>24.51</v>
       </c>
-      <c r="X13" s="3">
+      <c r="AA13" s="3">
         <v>20.56</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="AB13" s="3">
         <v>19.38</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="AC13" s="3">
         <v>17.34</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6">
         <v>45</v>
       </c>
-      <c r="C14" s="6">
+      <c r="F14" s="6">
         <v>44.7</v>
       </c>
-      <c r="D14" s="6">
+      <c r="G14" s="6">
         <v>44.6</v>
       </c>
-      <c r="E14" s="6">
+      <c r="H14" s="6">
         <v>44.4</v>
       </c>
-      <c r="F14" s="6">
+      <c r="I14" s="6">
         <v>43.3</v>
       </c>
-      <c r="G14" s="6">
+      <c r="J14" s="6">
         <v>42.2</v>
       </c>
-      <c r="H14" s="6">
+      <c r="K14" s="6">
         <v>43.8</v>
       </c>
-      <c r="I14" s="6">
+      <c r="L14" s="6">
         <v>40.200000000000003</v>
       </c>
-      <c r="J14" s="6">
+      <c r="M14" s="6">
         <v>38.4</v>
       </c>
-      <c r="K14" s="6">
+      <c r="N14" s="6">
         <v>38.299999999999997</v>
       </c>
-      <c r="L14" s="6">
+      <c r="O14" s="6">
         <v>37</v>
       </c>
-      <c r="M14" s="3">
+      <c r="P14" s="3">
         <v>37.18</v>
       </c>
-      <c r="N14" s="3">
+      <c r="Q14" s="3">
         <v>36.4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="R14" s="3">
         <v>34.229999999999997</v>
       </c>
-      <c r="P14" s="3">
+      <c r="S14" s="3">
         <v>30.92</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="T14" s="3">
         <v>27.43</v>
       </c>
-      <c r="R14" s="3">
+      <c r="U14" s="3">
         <v>24.49</v>
       </c>
-      <c r="S14" s="3">
+      <c r="V14" s="3">
         <v>22.81</v>
       </c>
-      <c r="T14" s="3">
+      <c r="W14" s="3">
         <v>22.46</v>
       </c>
-      <c r="U14" s="3">
+      <c r="X14" s="3">
         <v>21.03</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Y14" s="3">
         <v>18.04</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Z14" s="3">
         <v>15.34</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AA14" s="3">
         <v>14.23</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AB14" s="3">
         <v>13.82</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AC14" s="3">
         <v>12.05</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="6">
         <v>42.4</v>
       </c>
-      <c r="C15" s="6">
+      <c r="F15" s="6">
         <v>41</v>
       </c>
-      <c r="D15" s="6">
+      <c r="G15" s="6">
         <v>40</v>
       </c>
-      <c r="E15" s="6">
+      <c r="H15" s="6">
         <v>40.299999999999997</v>
       </c>
-      <c r="F15" s="6">
+      <c r="I15" s="6">
         <v>36.1</v>
       </c>
-      <c r="G15" s="6">
+      <c r="J15" s="6">
         <v>34.299999999999997</v>
       </c>
-      <c r="H15" s="6">
+      <c r="K15" s="6">
         <v>32.4</v>
       </c>
-      <c r="I15" s="6">
+      <c r="L15" s="6">
         <v>28.9</v>
       </c>
-      <c r="J15" s="6">
+      <c r="M15" s="6">
         <v>25.7</v>
       </c>
-      <c r="K15" s="6">
+      <c r="N15" s="6">
         <v>25.7</v>
       </c>
-      <c r="L15" s="6">
+      <c r="O15" s="6">
         <v>25.2</v>
       </c>
-      <c r="M15" s="3">
+      <c r="P15" s="3">
         <v>25.74</v>
       </c>
-      <c r="N15" s="3">
+      <c r="Q15" s="3">
         <v>24.7</v>
       </c>
-      <c r="O15" s="3">
+      <c r="R15" s="3">
         <v>23.69</v>
       </c>
-      <c r="P15" s="3">
+      <c r="S15" s="3">
         <v>22.62</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="T15" s="3">
         <v>23.87</v>
       </c>
-      <c r="R15" s="3">
+      <c r="U15" s="3">
         <v>25.23</v>
       </c>
-      <c r="S15" s="3">
+      <c r="V15" s="3">
         <v>23.8</v>
       </c>
-      <c r="T15" s="3">
+      <c r="W15" s="3">
         <v>22.28</v>
       </c>
-      <c r="U15" s="3">
+      <c r="X15" s="3">
         <v>21.75</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Y15" s="3">
         <v>20.14</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Z15" s="3">
         <v>18.739999999999998</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AA15" s="3">
         <v>18.23</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AB15" s="3">
         <v>17.93</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AC15" s="3">
         <v>15.97</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="6">
         <v>47.3</v>
       </c>
-      <c r="C16" s="6">
+      <c r="F16" s="6">
         <v>46.5</v>
       </c>
-      <c r="D16" s="6">
+      <c r="G16" s="6">
         <v>46</v>
       </c>
-      <c r="E16" s="6">
+      <c r="H16" s="6">
         <v>43.2</v>
       </c>
-      <c r="F16" s="6">
+      <c r="I16" s="6">
         <v>40.6</v>
       </c>
-      <c r="G16" s="6">
+      <c r="J16" s="6">
         <v>45.3</v>
       </c>
-      <c r="H16" s="6">
+      <c r="K16" s="6">
         <v>44.3</v>
       </c>
-      <c r="I16" s="6">
+      <c r="L16" s="6">
         <v>44.1</v>
       </c>
-      <c r="J16" s="6">
+      <c r="M16" s="6">
         <v>43.5</v>
       </c>
-      <c r="K16" s="6">
+      <c r="N16" s="6">
         <v>43.8</v>
       </c>
-      <c r="L16" s="6">
+      <c r="O16" s="6">
         <v>44.5</v>
       </c>
-      <c r="M16" s="3">
+      <c r="P16" s="3">
         <v>48.88</v>
       </c>
-      <c r="N16" s="3">
+      <c r="Q16" s="3">
         <v>47.47</v>
       </c>
-      <c r="O16" s="3">
+      <c r="R16" s="3">
         <v>46.79</v>
       </c>
-      <c r="P16" s="3">
+      <c r="S16" s="3">
         <v>45.88</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="T16" s="3">
         <v>42.94</v>
       </c>
-      <c r="R16" s="3">
+      <c r="U16" s="3">
         <v>38.159999999999997</v>
       </c>
-      <c r="S16" s="3">
+      <c r="V16" s="3">
         <v>33.94</v>
       </c>
-      <c r="T16" s="3">
+      <c r="W16" s="3">
         <v>31.35</v>
       </c>
-      <c r="U16" s="3">
+      <c r="X16" s="3">
         <v>28.64</v>
       </c>
-      <c r="V16" s="3">
+      <c r="Y16" s="3">
         <v>25.8</v>
       </c>
-      <c r="W16" s="3">
+      <c r="Z16" s="3">
         <v>23.31</v>
       </c>
-      <c r="X16" s="3">
+      <c r="AA16" s="3">
         <v>21.18</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="AB16" s="3">
         <v>19.760000000000002</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="AC16" s="3">
         <v>17.41</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="6">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="6">
         <v>44.6</v>
       </c>
-      <c r="D17" s="6">
+      <c r="G17" s="6">
         <v>47.4</v>
       </c>
-      <c r="E17" s="6">
+      <c r="H17" s="6">
         <v>44.7</v>
       </c>
-      <c r="F17" s="6">
+      <c r="I17" s="6">
         <v>40.700000000000003</v>
       </c>
-      <c r="G17" s="6">
+      <c r="J17" s="6">
         <v>36.700000000000003</v>
       </c>
-      <c r="H17" s="7">
+      <c r="K17" s="7">
         <v>32.9</v>
       </c>
-      <c r="I17" s="6">
+      <c r="L17" s="6">
         <v>31.3</v>
       </c>
-      <c r="J17" s="6">
+      <c r="M17" s="6">
         <v>30.9</v>
       </c>
-      <c r="K17" s="6">
+      <c r="N17" s="6">
         <v>31.9</v>
       </c>
-      <c r="L17" s="6">
+      <c r="O17" s="6">
         <v>30</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>31.42</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>31.26</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>34.26</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>32.58</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>27.1</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>17.600000000000001</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>15.35</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>17.38</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>15.28</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>13.48</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>12.24</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>10.59</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AB17" s="3">
         <v>11.29</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AC17" s="3">
         <v>10.24</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="6">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="6">
         <v>40.299999999999997</v>
       </c>
-      <c r="D18" s="6">
+      <c r="G18" s="6">
         <v>40.200000000000003</v>
       </c>
-      <c r="E18" s="6">
+      <c r="H18" s="6">
         <v>42</v>
       </c>
-      <c r="F18" s="6">
+      <c r="I18" s="6">
         <v>37.299999999999997</v>
       </c>
-      <c r="G18" s="6">
+      <c r="J18" s="6">
         <v>40</v>
       </c>
-      <c r="H18" s="6">
+      <c r="K18" s="6">
         <v>39</v>
       </c>
-      <c r="I18" s="6">
+      <c r="L18" s="6">
         <v>37.4</v>
       </c>
-      <c r="J18" s="6">
+      <c r="M18" s="6">
         <v>37.799999999999997</v>
       </c>
-      <c r="K18" s="6">
+      <c r="N18" s="6">
         <v>39.5</v>
       </c>
-      <c r="L18" s="6">
+      <c r="O18" s="6">
         <v>38.299999999999997</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>40.69</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>40.75</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>41.13</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>39.18</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>35.86</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>31.86</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>30</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>28.04</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>25.92</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>24.37</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>22.97</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>21.62</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>20.65</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -2859,211 +2946,308 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="3">
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="3">
         <v>53.78</v>
       </c>
-      <c r="N19" s="3">
+      <c r="Q19" s="3">
         <v>53.71</v>
       </c>
-      <c r="O19" s="3">
+      <c r="R19" s="3">
         <v>50.13</v>
       </c>
-      <c r="P19" s="3">
+      <c r="S19" s="3">
         <v>44.91</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="T19" s="3">
         <v>40.57</v>
       </c>
-      <c r="R19" s="3">
+      <c r="U19" s="3">
         <v>37.01</v>
       </c>
-      <c r="S19" s="3">
+      <c r="V19" s="3">
         <v>34</v>
       </c>
-      <c r="T19" s="3">
+      <c r="W19" s="3">
         <v>31.57</v>
       </c>
-      <c r="U19" s="3">
+      <c r="X19" s="3">
         <v>29.67</v>
       </c>
-      <c r="V19" s="3">
+      <c r="Y19" s="3">
         <v>26.41</v>
       </c>
-      <c r="W19" s="3">
+      <c r="Z19" s="3">
         <v>24.37</v>
       </c>
-      <c r="X19" s="3">
+      <c r="AA19" s="3">
         <v>22.12</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="AB19" s="3">
         <v>21.52</v>
       </c>
-      <c r="Z19" s="3">
+      <c r="AC19" s="3">
         <v>20.010000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="6">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="6">
         <v>43.7</v>
       </c>
-      <c r="F20" s="6">
+      <c r="I20" s="6">
         <v>41.7</v>
       </c>
-      <c r="G20" s="6">
+      <c r="J20" s="6">
         <v>44.3</v>
       </c>
-      <c r="H20" s="6">
+      <c r="K20" s="6">
         <v>44.1</v>
       </c>
-      <c r="I20" s="6">
+      <c r="L20" s="6">
         <v>42</v>
       </c>
-      <c r="J20" s="6">
+      <c r="M20" s="6">
         <v>41.9</v>
       </c>
-      <c r="K20" s="6">
+      <c r="N20" s="6">
         <v>43.8</v>
       </c>
-      <c r="L20" s="6">
+      <c r="O20" s="6">
         <v>44.5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>52.23</v>
       </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
         <v>50.79</v>
       </c>
-      <c r="O20" s="3">
+      <c r="R20" s="3">
         <v>48.62</v>
       </c>
-      <c r="P20" s="3">
+      <c r="S20" s="3">
         <v>46.99</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>46.06</v>
       </c>
-      <c r="R20" s="3">
+      <c r="U20" s="3">
         <v>45.59</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>43.06</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>39.9</v>
       </c>
-      <c r="U20" s="3">
+      <c r="X20" s="3">
         <v>37.9</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Y20" s="3">
         <v>35.69</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Z20" s="3">
         <v>32.35</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AA20" s="3">
         <v>28.19</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AB20" s="3">
         <v>25.32</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AC20" s="3">
         <v>23.58</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="13">
         <v>43.4</v>
       </c>
-      <c r="C21" s="13">
+      <c r="F21" s="13">
         <v>38.9</v>
       </c>
-      <c r="D21" s="13">
+      <c r="G21" s="13">
         <v>37.6</v>
       </c>
-      <c r="E21" s="13">
+      <c r="H21" s="13">
         <v>36.5</v>
       </c>
-      <c r="F21" s="13">
+      <c r="I21" s="13">
         <v>31.9</v>
       </c>
-      <c r="G21" s="13">
+      <c r="J21" s="13">
         <v>30.1</v>
       </c>
-      <c r="H21" s="13">
+      <c r="K21" s="13">
         <v>28.6</v>
       </c>
-      <c r="I21" s="13">
+      <c r="L21" s="13">
         <v>25.8</v>
       </c>
-      <c r="J21" s="13">
+      <c r="M21" s="13">
         <v>22.3</v>
       </c>
-      <c r="K21" s="13">
+      <c r="N21" s="13">
         <v>21.6</v>
       </c>
-      <c r="L21" s="13">
+      <c r="O21" s="13">
         <v>21.1</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>21.28</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>21.8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="R21" s="3">
         <v>21.75</v>
       </c>
-      <c r="P21" s="3">
+      <c r="S21" s="3">
         <v>20.57</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="T21" s="3">
         <v>20.32</v>
       </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <v>20.6</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
         <v>18.07</v>
       </c>
-      <c r="T21" s="3">
+      <c r="W21" s="3">
         <v>17.93</v>
       </c>
-      <c r="U21" s="3">
+      <c r="X21" s="3">
         <v>17.739999999999998</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Y21" s="3">
         <v>16.98</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Z21" s="3">
         <v>15.53</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AA21" s="3">
         <v>14.66</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AB21" s="3">
         <v>14.22</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AC21" s="3">
         <v>12.66</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="16">
+        <v>48.1</v>
+      </c>
+      <c r="C22" s="16">
+        <v>47.7</v>
+      </c>
+      <c r="D22" s="16">
+        <v>47.2</v>
+      </c>
+      <c r="E22" s="11">
+        <v>46.1</v>
+      </c>
+      <c r="F22" s="11">
+        <v>44.3</v>
+      </c>
+      <c r="G22" s="11">
+        <v>42.4</v>
+      </c>
+      <c r="H22" s="11">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="I22" s="11">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="J22" s="11">
+        <v>35</v>
+      </c>
+      <c r="K22" s="11">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="L22" s="11">
+        <v>30.9</v>
+      </c>
+      <c r="M22" s="11">
+        <v>26.9</v>
+      </c>
+      <c r="N22" s="11">
+        <v>26.1</v>
+      </c>
+      <c r="O22" s="11">
+        <v>26.4</v>
+      </c>
+      <c r="P22" s="3">
+        <v>25.74</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>24.7</v>
+      </c>
+      <c r="R22" s="3">
+        <v>23.69</v>
+      </c>
+      <c r="S22" s="3">
+        <v>22.62</v>
+      </c>
+      <c r="T22" s="3">
+        <v>23.87</v>
+      </c>
+      <c r="U22" s="3">
+        <v>25.23</v>
+      </c>
+      <c r="V22" s="3">
+        <v>23.8</v>
+      </c>
+      <c r="W22" s="3">
+        <v>22.28</v>
+      </c>
+      <c r="X22" s="3">
+        <v>21.75</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>20.14</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>18.23</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>17.93</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>15.97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -3072,84 +3256,87 @@
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B26" s="12"/>
-      <c r="D26" s="3"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B27" s="12"/>
-      <c r="D27" s="3"/>
-      <c r="M27" s="12"/>
-      <c r="O27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="M28" s="12"/>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="M29" s="12"/>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="E26" s="12"/>
+      <c r="G26" s="3"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="E27" s="12"/>
+      <c r="G27" s="3"/>
+      <c r="P27" s="12"/>
+      <c r="R27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="P28" s="12"/>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="P29" s="12"/>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="M31" s="12"/>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="M32" s="12"/>
-      <c r="O32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+      <c r="AA30" s="12"/>
+      <c r="AB30" s="12"/>
+      <c r="AC30" s="12"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="P31" s="12"/>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="P32" s="12"/>
+      <c r="R32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
-    </row>
-    <row r="33" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M33" s="12"/>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M34" s="12"/>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M35" s="12"/>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="36" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M36" s="12"/>
-      <c r="O36" s="3"/>
-    </row>
-    <row r="37" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M37" s="12"/>
-      <c r="O37" s="3"/>
-    </row>
-    <row r="38" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M38" s="12"/>
-      <c r="O38" s="3"/>
-    </row>
-    <row r="39" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M39" s="12"/>
-      <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M40" s="12"/>
-      <c r="O40" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+    </row>
+    <row r="33" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P33" s="12"/>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P34" s="12"/>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P35" s="12"/>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="36" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P36" s="12"/>
+      <c r="R36" s="3"/>
+    </row>
+    <row r="37" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P37" s="12"/>
+      <c r="R37" s="3"/>
+    </row>
+    <row r="38" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P38" s="12"/>
+      <c r="R38" s="3"/>
+    </row>
+    <row r="39" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P39" s="12"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P40" s="12"/>
+      <c r="R40" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3159,14 +3346,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40E0A31-8EE1-4474-96EA-571AB8EBD4C3}">
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
-    <col min="2" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="29" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
@@ -3181,562 +3368,592 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="O3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="W3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="X3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="Y3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="AB3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="AC3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="6">
         <v>29.4</v>
       </c>
-      <c r="C4" s="6">
+      <c r="F4" s="6">
         <v>29.1</v>
       </c>
-      <c r="D4" s="6">
+      <c r="G4" s="6">
         <v>29.8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="H4" s="6">
         <v>28.3</v>
       </c>
-      <c r="F4" s="6">
+      <c r="I4" s="6">
         <v>29.7</v>
       </c>
-      <c r="G4" s="6">
+      <c r="J4" s="6">
         <v>26</v>
       </c>
-      <c r="H4" s="6">
+      <c r="K4" s="6">
         <v>24.6</v>
       </c>
-      <c r="I4" s="6">
+      <c r="L4" s="6">
         <v>21.9</v>
       </c>
-      <c r="J4" s="6">
+      <c r="M4" s="6">
         <v>21.1</v>
       </c>
-      <c r="K4" s="6">
+      <c r="N4" s="6">
         <v>19.8</v>
       </c>
-      <c r="L4" s="6">
+      <c r="O4" s="6">
         <v>16.100000000000001</v>
       </c>
-      <c r="M4" s="3">
+      <c r="P4" s="3">
         <v>13.46</v>
       </c>
-      <c r="N4" s="3">
+      <c r="Q4" s="3">
         <v>11.36</v>
       </c>
-      <c r="O4" s="3">
+      <c r="R4" s="3">
         <v>9.23</v>
       </c>
-      <c r="P4" s="3">
+      <c r="S4" s="3">
         <v>7.45</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="T4" s="3">
         <v>6.34</v>
       </c>
-      <c r="R4" s="3">
+      <c r="U4" s="3">
         <v>5.59</v>
       </c>
-      <c r="S4" s="3">
+      <c r="V4" s="3">
         <v>5.2</v>
       </c>
-      <c r="T4" s="3">
+      <c r="W4" s="3">
         <v>4.84</v>
       </c>
-      <c r="U4" s="3">
+      <c r="X4" s="3">
         <v>4.83</v>
       </c>
-      <c r="V4" s="3">
+      <c r="Y4" s="3">
         <v>4.8</v>
       </c>
-      <c r="W4" s="3">
+      <c r="Z4" s="3">
         <v>5.16</v>
       </c>
-      <c r="X4" s="3">
+      <c r="AA4" s="3">
         <v>5.3</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="AB4" s="3">
         <v>5.72</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="AC4" s="3">
         <v>6.58</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="6">
         <v>29.3</v>
       </c>
-      <c r="C5" s="6">
+      <c r="F5" s="6">
         <v>28.8</v>
       </c>
-      <c r="D5" s="6">
+      <c r="G5" s="6">
         <v>28.6</v>
       </c>
-      <c r="E5" s="6">
+      <c r="H5" s="6">
         <v>27.2</v>
       </c>
-      <c r="F5" s="6">
+      <c r="I5" s="6">
         <v>29</v>
       </c>
-      <c r="G5" s="6">
+      <c r="J5" s="6">
         <v>25.2</v>
       </c>
-      <c r="H5" s="6">
+      <c r="K5" s="6">
         <v>23.6</v>
       </c>
-      <c r="I5" s="6">
+      <c r="L5" s="6">
         <v>21.5</v>
       </c>
-      <c r="J5" s="6">
+      <c r="M5" s="6">
         <v>19.2</v>
       </c>
-      <c r="K5" s="6">
+      <c r="N5" s="6">
         <v>17.399999999999999</v>
       </c>
-      <c r="L5" s="6">
+      <c r="O5" s="6">
         <v>13.2</v>
       </c>
-      <c r="M5" s="3">
+      <c r="P5" s="3">
         <v>11.47</v>
       </c>
-      <c r="N5" s="3">
+      <c r="Q5" s="3">
         <v>9.66</v>
       </c>
-      <c r="O5" s="3">
+      <c r="R5" s="3">
         <v>8.23</v>
       </c>
-      <c r="P5" s="3">
+      <c r="S5" s="3">
         <v>7.07</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="T5" s="3">
         <v>5.73</v>
       </c>
-      <c r="R5" s="3">
+      <c r="U5" s="3">
         <v>4.6100000000000003</v>
       </c>
-      <c r="S5" s="3">
+      <c r="V5" s="3">
         <v>4.03</v>
       </c>
-      <c r="T5" s="3">
+      <c r="W5" s="3">
         <v>3.8</v>
       </c>
-      <c r="U5" s="3">
+      <c r="X5" s="3">
         <v>3.73</v>
       </c>
-      <c r="V5" s="3">
+      <c r="Y5" s="3">
         <v>3.91</v>
       </c>
-      <c r="W5" s="3">
+      <c r="Z5" s="3">
         <v>3.88</v>
       </c>
-      <c r="X5" s="3">
+      <c r="AA5" s="3">
         <v>3.99</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="AB5" s="3">
         <v>4.33</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="AC5" s="3">
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6">
         <v>35.4</v>
       </c>
-      <c r="D6" s="6">
+      <c r="G6" s="6">
         <v>34</v>
       </c>
-      <c r="E6" s="6">
+      <c r="H6" s="6">
         <v>33</v>
       </c>
-      <c r="F6" s="6">
+      <c r="I6" s="6">
         <v>40.799999999999997</v>
       </c>
-      <c r="G6" s="6">
+      <c r="J6" s="6">
         <v>33.700000000000003</v>
       </c>
-      <c r="H6" s="6">
+      <c r="K6" s="6">
         <v>32.6</v>
       </c>
-      <c r="I6" s="6">
+      <c r="L6" s="6">
         <v>31.7</v>
       </c>
-      <c r="J6" s="6">
+      <c r="M6" s="6">
         <v>30.7</v>
       </c>
-      <c r="K6" s="6">
+      <c r="N6" s="6">
         <v>28.5</v>
       </c>
-      <c r="L6" s="6">
+      <c r="O6" s="6">
         <v>26.5</v>
       </c>
-      <c r="M6" s="3">
+      <c r="P6" s="3">
         <v>24.83</v>
       </c>
-      <c r="N6" s="3">
+      <c r="Q6" s="3">
         <v>21.72</v>
       </c>
-      <c r="O6" s="3">
+      <c r="R6" s="3">
         <v>18.13</v>
       </c>
-      <c r="P6" s="3">
+      <c r="S6" s="3">
         <v>16.850000000000001</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="T6" s="3">
         <v>14.28</v>
       </c>
-      <c r="R6" s="3">
+      <c r="U6" s="3">
         <v>13</v>
       </c>
-      <c r="S6" s="3">
+      <c r="V6" s="3">
         <v>12.11</v>
       </c>
-      <c r="T6" s="3">
+      <c r="W6" s="3">
         <v>9.23</v>
       </c>
-      <c r="U6" s="3">
+      <c r="X6" s="3">
         <v>8.49</v>
       </c>
-      <c r="V6" s="3">
+      <c r="Y6" s="3">
         <v>7.06</v>
       </c>
-      <c r="W6" s="3">
+      <c r="Z6" s="3">
         <v>6</v>
       </c>
-      <c r="X6" s="3">
+      <c r="AA6" s="3">
         <v>5.6</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="AB6" s="3">
         <v>5.26</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="AC6" s="3">
         <v>5.15</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
         <v>26.6</v>
       </c>
-      <c r="D7" s="6">
+      <c r="G7" s="6">
         <v>26.8</v>
       </c>
-      <c r="E7" s="6">
+      <c r="H7" s="6">
         <v>26</v>
       </c>
-      <c r="F7" s="6">
+      <c r="I7" s="6">
         <v>25.1</v>
       </c>
-      <c r="G7" s="6">
+      <c r="J7" s="6">
         <v>23.7</v>
       </c>
-      <c r="H7" s="6">
+      <c r="K7" s="6">
         <v>22.4</v>
       </c>
-      <c r="I7" s="6">
+      <c r="L7" s="6">
         <v>22.5</v>
       </c>
-      <c r="J7" s="6">
+      <c r="M7" s="6">
         <v>21.6</v>
       </c>
-      <c r="K7" s="6">
+      <c r="N7" s="6">
         <v>20.3</v>
       </c>
-      <c r="L7" s="6">
+      <c r="O7" s="6">
         <v>20.8</v>
       </c>
-      <c r="M7" s="3">
+      <c r="P7" s="3">
         <v>16.510000000000002</v>
       </c>
-      <c r="N7" s="3">
+      <c r="Q7" s="3">
         <v>13.76</v>
       </c>
-      <c r="O7" s="3">
+      <c r="R7" s="3">
         <v>11.19</v>
       </c>
-      <c r="P7" s="3">
+      <c r="S7" s="3">
         <v>9.41</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="T7" s="3">
         <v>7.84</v>
       </c>
-      <c r="R7" s="3">
+      <c r="U7" s="3">
         <v>6.66</v>
       </c>
-      <c r="S7" s="3">
+      <c r="V7" s="3">
         <v>5.9</v>
       </c>
-      <c r="T7" s="3">
+      <c r="W7" s="3">
         <v>6.06</v>
       </c>
-      <c r="U7" s="3">
+      <c r="X7" s="3">
         <v>5.88</v>
       </c>
-      <c r="V7" s="3">
+      <c r="Y7" s="3">
         <v>5.54</v>
       </c>
-      <c r="W7" s="3">
+      <c r="Z7" s="3">
         <v>5.39</v>
       </c>
-      <c r="X7" s="3">
+      <c r="AA7" s="3">
         <v>5.05</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="AB7" s="3">
         <v>5.04</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="AC7" s="3">
         <v>5.32</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="6">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6">
         <v>30.2</v>
       </c>
-      <c r="G8" s="6">
+      <c r="J8" s="6">
         <v>28.9</v>
       </c>
-      <c r="H8" s="6">
+      <c r="K8" s="6">
         <v>28.2</v>
       </c>
-      <c r="I8" s="6">
+      <c r="L8" s="6">
         <v>25.7</v>
       </c>
-      <c r="J8" s="6">
+      <c r="M8" s="6">
         <v>25.6</v>
       </c>
-      <c r="K8" s="6">
+      <c r="N8" s="6">
         <v>24</v>
       </c>
-      <c r="L8" s="6">
+      <c r="O8" s="6">
         <v>20</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>18.86</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>16.75</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>14.39</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>12.43</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>10.72</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>9.17</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>7.7</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>6.48</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>5.49</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>5.0599999999999996</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>4.95</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AA8" s="3">
         <v>4.87</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>4.8600000000000003</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>4.87</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="11">
         <v>28.520000000000003</v>
       </c>
-      <c r="C9" s="11">
+      <c r="F9" s="11">
         <v>27.640000000000004</v>
       </c>
-      <c r="D9" s="11">
+      <c r="G9" s="11">
         <v>27.240000000000002</v>
       </c>
-      <c r="E9" s="11">
+      <c r="H9" s="11">
         <v>26.879999999999995</v>
       </c>
-      <c r="F9" s="11">
+      <c r="I9" s="11">
         <v>26.580000000000002</v>
       </c>
-      <c r="G9" s="11">
+      <c r="J9" s="11">
         <v>26.32</v>
       </c>
-      <c r="H9" s="11">
+      <c r="K9" s="11">
         <v>26.119999999999997</v>
       </c>
-      <c r="I9" s="11">
+      <c r="L9" s="11">
         <v>25.32</v>
       </c>
-      <c r="J9" s="11">
+      <c r="M9" s="11">
         <v>23.62</v>
       </c>
-      <c r="K9" s="11">
+      <c r="N9" s="11">
         <v>21.919999999999998</v>
       </c>
-      <c r="L9" s="11">
+      <c r="O9" s="11">
         <v>19.559999999999999</v>
       </c>
-      <c r="M9" s="14">
+      <c r="P9" s="14">
         <v>16.309999999999999</v>
       </c>
-      <c r="N9" s="14">
+      <c r="Q9" s="14">
         <v>14.6</v>
       </c>
-      <c r="O9" s="14">
+      <c r="R9" s="14">
         <v>12.95</v>
       </c>
-      <c r="P9" s="14">
+      <c r="S9" s="14">
         <v>11.32</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="T9" s="14">
         <v>10.050000000000001</v>
       </c>
-      <c r="R9" s="14">
+      <c r="U9" s="14">
         <v>9.1199999999999992</v>
       </c>
-      <c r="S9" s="14">
+      <c r="V9" s="14">
         <v>8.23</v>
       </c>
-      <c r="T9" s="14">
+      <c r="W9" s="14">
         <v>7.37</v>
       </c>
-      <c r="U9" s="14">
+      <c r="X9" s="14">
         <v>6.8</v>
       </c>
-      <c r="V9" s="14">
+      <c r="Y9" s="14">
         <v>6.41</v>
       </c>
-      <c r="W9" s="14">
+      <c r="Z9" s="14">
         <v>6.11</v>
       </c>
-      <c r="X9" s="14">
+      <c r="AA9" s="14">
         <v>5.82</v>
       </c>
-      <c r="Y9" s="14">
+      <c r="AB9" s="14">
         <v>5.89</v>
       </c>
-      <c r="Z9" s="14">
+      <c r="AC9" s="14">
         <v>6.26</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -3745,118 +3962,124 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
-      <c r="M10" s="3">
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="3">
         <v>11.57</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>11.06</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>10.24</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>9.73</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>9.1300000000000008</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>8.69</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>8.14</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>7.07</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>6.15</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>5.56</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>5.23</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>5.19</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>5.21</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>5.46</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="6">
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6">
         <v>28.8</v>
       </c>
-      <c r="L11" s="6">
+      <c r="O11" s="6">
         <v>24.7</v>
       </c>
-      <c r="M11" s="3">
+      <c r="P11" s="3">
         <v>19.86</v>
       </c>
-      <c r="N11" s="3">
+      <c r="Q11" s="3">
         <v>18.350000000000001</v>
       </c>
-      <c r="O11" s="3">
+      <c r="R11" s="3">
         <v>16.3</v>
       </c>
-      <c r="P11" s="3">
+      <c r="S11" s="3">
         <v>14.63</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="T11" s="3">
         <v>14.33</v>
       </c>
-      <c r="R11" s="3">
+      <c r="U11" s="3">
         <v>11.85</v>
       </c>
-      <c r="S11" s="3">
+      <c r="V11" s="3">
         <v>10.17</v>
       </c>
-      <c r="T11" s="3">
+      <c r="W11" s="3">
         <v>8.58</v>
       </c>
-      <c r="U11" s="3">
+      <c r="X11" s="3">
         <v>7.16</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Y11" s="3">
         <v>6.01</v>
       </c>
-      <c r="W11" s="3">
+      <c r="Z11" s="3">
         <v>5.68</v>
       </c>
-      <c r="X11" s="3">
+      <c r="AA11" s="3">
         <v>6.29</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="AB11" s="3">
         <v>6.46</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="AC11" s="3">
         <v>6.1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -3865,530 +4088,551 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
-      <c r="M12" s="3">
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="3">
         <v>25.14</v>
       </c>
-      <c r="N12" s="3">
+      <c r="Q12" s="3">
         <v>23.6</v>
       </c>
-      <c r="O12" s="3">
+      <c r="R12" s="3">
         <v>22.06</v>
       </c>
-      <c r="P12" s="3">
+      <c r="S12" s="3">
         <v>20.27</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="T12" s="3">
         <v>18.43</v>
       </c>
-      <c r="R12" s="3">
+      <c r="U12" s="3">
         <v>16.43</v>
       </c>
-      <c r="S12" s="3">
+      <c r="V12" s="3">
         <v>14.75</v>
       </c>
-      <c r="T12" s="3">
+      <c r="W12" s="3">
         <v>13.14</v>
       </c>
-      <c r="U12" s="3">
+      <c r="X12" s="3">
         <v>11.35</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Y12" s="3">
         <v>10.19</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Z12" s="3">
         <v>9.36</v>
       </c>
-      <c r="X12" s="3">
+      <c r="AA12" s="3">
         <v>8.48</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AB12" s="3">
         <v>7.86</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AC12" s="3">
         <v>7.6</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6">
         <v>29.7</v>
       </c>
-      <c r="D13" s="6">
+      <c r="G13" s="6">
         <v>31.4</v>
       </c>
-      <c r="E13" s="6">
+      <c r="H13" s="6">
         <v>31.1</v>
       </c>
-      <c r="F13" s="6">
+      <c r="I13" s="6">
         <v>41.2</v>
       </c>
-      <c r="G13" s="6">
+      <c r="J13" s="6">
         <v>32.799999999999997</v>
       </c>
-      <c r="H13" s="6">
+      <c r="K13" s="6">
         <v>34.1</v>
       </c>
-      <c r="I13" s="6">
+      <c r="L13" s="6">
         <v>32.700000000000003</v>
       </c>
-      <c r="J13" s="6">
+      <c r="M13" s="6">
         <v>29.6</v>
       </c>
-      <c r="K13" s="6">
+      <c r="N13" s="6">
         <v>28.5</v>
       </c>
-      <c r="L13" s="6">
+      <c r="O13" s="6">
         <v>22.8</v>
       </c>
-      <c r="M13" s="3">
+      <c r="P13" s="3">
         <v>20.77</v>
       </c>
-      <c r="N13" s="3">
+      <c r="Q13" s="3">
         <v>18.88</v>
       </c>
-      <c r="O13" s="3">
+      <c r="R13" s="3">
         <v>17.27</v>
       </c>
-      <c r="P13" s="3">
+      <c r="S13" s="3">
         <v>16.02</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="T13" s="3">
         <v>14.5</v>
       </c>
-      <c r="R13" s="3">
+      <c r="U13" s="3">
         <v>12.56</v>
       </c>
-      <c r="S13" s="3">
+      <c r="V13" s="3">
         <v>12.8</v>
       </c>
-      <c r="T13" s="3">
+      <c r="W13" s="3">
         <v>8.91</v>
       </c>
-      <c r="U13" s="3">
+      <c r="X13" s="3">
         <v>7.25</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Y13" s="3">
         <v>6.64</v>
       </c>
-      <c r="W13" s="3">
+      <c r="Z13" s="3">
         <v>6.73</v>
       </c>
-      <c r="X13" s="3">
+      <c r="AA13" s="3">
         <v>7.51</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="AB13" s="3">
         <v>7.15</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="AC13" s="3">
         <v>7.44</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6">
         <v>30.3</v>
       </c>
-      <c r="C14" s="6">
+      <c r="F14" s="6">
         <v>31.6</v>
       </c>
-      <c r="D14" s="6">
+      <c r="G14" s="6">
         <v>33.200000000000003</v>
       </c>
-      <c r="E14" s="6">
+      <c r="H14" s="6">
         <v>31.5</v>
       </c>
-      <c r="F14" s="6">
+      <c r="I14" s="6">
         <v>31</v>
       </c>
-      <c r="G14" s="6">
+      <c r="J14" s="6">
         <v>31.3</v>
       </c>
-      <c r="H14" s="6">
+      <c r="K14" s="6">
         <v>26.4</v>
       </c>
-      <c r="I14" s="6">
+      <c r="L14" s="6">
         <v>24.5</v>
       </c>
-      <c r="J14" s="6">
+      <c r="M14" s="6">
         <v>23.8</v>
       </c>
-      <c r="K14" s="6">
+      <c r="N14" s="6">
         <v>20.100000000000001</v>
       </c>
-      <c r="L14" s="6">
+      <c r="O14" s="6">
         <v>17.5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="P14" s="3">
         <v>13.61</v>
       </c>
-      <c r="N14" s="3">
+      <c r="Q14" s="3">
         <v>11.82</v>
       </c>
-      <c r="O14" s="3">
+      <c r="R14" s="3">
         <v>10.6</v>
       </c>
-      <c r="P14" s="3">
+      <c r="S14" s="3">
         <v>9.11</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="T14" s="3">
         <v>7.94</v>
       </c>
-      <c r="R14" s="3">
+      <c r="U14" s="3">
         <v>6.58</v>
       </c>
-      <c r="S14" s="3">
+      <c r="V14" s="3">
         <v>5.87</v>
       </c>
-      <c r="T14" s="3">
+      <c r="W14" s="3">
         <v>5.48</v>
       </c>
-      <c r="U14" s="3">
+      <c r="X14" s="3">
         <v>5.19</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Y14" s="3">
         <v>5.13</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Z14" s="3">
         <v>5.0599999999999996</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AA14" s="3">
         <v>5.48</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AB14" s="3">
         <v>5.98</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AC14" s="3">
         <v>6.18</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="6">
         <v>23.8</v>
       </c>
-      <c r="C15" s="6">
+      <c r="F15" s="6">
         <v>21.6</v>
       </c>
-      <c r="D15" s="6">
+      <c r="G15" s="6">
         <v>20.100000000000001</v>
       </c>
-      <c r="E15" s="6">
+      <c r="H15" s="6">
         <v>17.7</v>
       </c>
-      <c r="F15" s="6">
+      <c r="I15" s="6">
         <v>16.5</v>
       </c>
-      <c r="G15" s="6">
+      <c r="J15" s="6">
         <v>14</v>
       </c>
-      <c r="H15" s="6">
+      <c r="K15" s="6">
         <v>13.1</v>
       </c>
-      <c r="I15" s="6">
+      <c r="L15" s="6">
         <v>11.6</v>
       </c>
-      <c r="J15" s="6">
+      <c r="M15" s="6">
         <v>11.6</v>
       </c>
-      <c r="K15" s="6">
+      <c r="N15" s="6">
         <v>10.4</v>
       </c>
-      <c r="L15" s="6">
+      <c r="O15" s="6">
         <v>9.6</v>
       </c>
-      <c r="M15" s="3">
+      <c r="P15" s="3">
         <v>9.24</v>
       </c>
-      <c r="N15" s="3">
+      <c r="Q15" s="3">
         <v>8.77</v>
       </c>
-      <c r="O15" s="3">
+      <c r="R15" s="3">
         <v>8.6999999999999993</v>
       </c>
-      <c r="P15" s="3">
+      <c r="S15" s="3">
         <v>9.0299999999999994</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="T15" s="3">
         <v>9.27</v>
       </c>
-      <c r="R15" s="3">
+      <c r="U15" s="3">
         <v>8.9700000000000006</v>
       </c>
-      <c r="S15" s="3">
+      <c r="V15" s="3">
         <v>8.8000000000000007</v>
       </c>
-      <c r="T15" s="3">
+      <c r="W15" s="3">
         <v>8.06</v>
       </c>
-      <c r="U15" s="3">
+      <c r="X15" s="3">
         <v>7.66</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Y15" s="3">
         <v>7.54</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Z15" s="3">
         <v>7.57</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AA15" s="3">
         <v>7.55</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AB15" s="3">
         <v>7.62</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AC15" s="3">
         <v>7.65</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="6">
         <v>34.4</v>
       </c>
-      <c r="C16" s="6">
+      <c r="F16" s="6">
         <v>33.4</v>
       </c>
-      <c r="D16" s="6">
+      <c r="G16" s="6">
         <v>32.9</v>
       </c>
-      <c r="E16" s="6">
+      <c r="H16" s="6">
         <v>46.6</v>
       </c>
-      <c r="F16" s="6">
+      <c r="I16" s="6">
         <v>48.3</v>
       </c>
-      <c r="G16" s="6">
+      <c r="J16" s="6">
         <v>28.4</v>
       </c>
-      <c r="H16" s="6">
+      <c r="K16" s="6">
         <v>26.7</v>
       </c>
-      <c r="I16" s="6">
+      <c r="L16" s="6">
         <v>26.7</v>
       </c>
-      <c r="J16" s="6">
+      <c r="M16" s="6">
         <v>23.5</v>
       </c>
-      <c r="K16" s="6">
+      <c r="N16" s="6">
         <v>21.8</v>
       </c>
-      <c r="L16" s="6">
+      <c r="O16" s="6">
         <v>17.8</v>
       </c>
-      <c r="M16" s="3">
+      <c r="P16" s="3">
         <v>19.87</v>
       </c>
-      <c r="N16" s="3">
+      <c r="Q16" s="3">
         <v>15.76</v>
       </c>
-      <c r="O16" s="3">
+      <c r="R16" s="3">
         <v>12.95</v>
       </c>
-      <c r="P16" s="3">
+      <c r="S16" s="3">
         <v>10.89</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="T16" s="3">
         <v>9.31</v>
       </c>
-      <c r="R16" s="3">
+      <c r="U16" s="3">
         <v>7.62</v>
       </c>
-      <c r="S16" s="3">
+      <c r="V16" s="3">
         <v>6.61</v>
       </c>
-      <c r="T16" s="3">
+      <c r="W16" s="3">
         <v>6.19</v>
       </c>
-      <c r="U16" s="3">
+      <c r="X16" s="3">
         <v>5.97</v>
       </c>
-      <c r="V16" s="3">
+      <c r="Y16" s="3">
         <v>5.58</v>
       </c>
-      <c r="W16" s="3">
+      <c r="Z16" s="3">
         <v>5.47</v>
       </c>
-      <c r="X16" s="3">
+      <c r="AA16" s="3">
         <v>5.63</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="AB16" s="3">
         <v>5.7</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="AC16" s="3">
         <v>5.96</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="6">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="6">
         <v>23.7</v>
       </c>
-      <c r="D17" s="6">
+      <c r="G17" s="6">
         <v>23.3</v>
       </c>
-      <c r="E17" s="6">
+      <c r="H17" s="6">
         <v>21.4</v>
       </c>
-      <c r="F17" s="6">
+      <c r="I17" s="6">
         <v>22.2</v>
       </c>
-      <c r="G17" s="6">
+      <c r="J17" s="6">
         <v>19.3</v>
       </c>
-      <c r="H17" s="6">
+      <c r="K17" s="6">
         <v>15.2</v>
       </c>
-      <c r="I17" s="6">
+      <c r="L17" s="6">
         <v>13.3</v>
       </c>
-      <c r="J17" s="6">
+      <c r="M17" s="6">
         <v>12.7</v>
       </c>
-      <c r="K17" s="6">
+      <c r="N17" s="6">
         <v>10.9</v>
       </c>
-      <c r="L17" s="6">
+      <c r="O17" s="6">
         <v>8.6999999999999993</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>10.59</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>9.43</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>8.6300000000000008</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>7.67</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>6.72</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>6.26</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>6.34</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>6.74</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>7.23</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>7.28</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>7.28</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>7.82</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AB17" s="3">
         <v>8.39</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AC17" s="3">
         <v>9.68</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="6">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="6">
         <v>21</v>
       </c>
-      <c r="D18" s="6">
+      <c r="G18" s="6">
         <v>19.7</v>
       </c>
-      <c r="E18" s="6">
+      <c r="H18" s="6">
         <v>19</v>
       </c>
-      <c r="F18" s="6">
+      <c r="I18" s="6">
         <v>17.3</v>
       </c>
-      <c r="G18" s="6">
+      <c r="J18" s="6">
         <v>17.3</v>
       </c>
-      <c r="H18" s="6">
+      <c r="K18" s="6">
         <v>16.600000000000001</v>
       </c>
-      <c r="I18" s="6">
+      <c r="L18" s="6">
         <v>15.1</v>
       </c>
-      <c r="J18" s="6">
+      <c r="M18" s="6">
         <v>12.6</v>
       </c>
-      <c r="K18" s="6">
+      <c r="N18" s="6">
         <v>12.7</v>
       </c>
-      <c r="L18" s="6">
+      <c r="O18" s="6">
         <v>10.8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>12.09</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>10.61</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>9.1</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>8.19</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>6.99</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>5.71</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>5.22</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>5.17</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>5.05</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>4.9800000000000004</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>4.71</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>4.58</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>4.6399999999999997</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>4.74</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -4397,213 +4641,312 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="3">
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="3">
         <v>20.72</v>
       </c>
-      <c r="N19" s="3">
+      <c r="Q19" s="3">
         <v>17.91</v>
       </c>
-      <c r="O19" s="3">
+      <c r="R19" s="3">
         <v>14.89</v>
       </c>
-      <c r="P19" s="3">
+      <c r="S19" s="3">
         <v>12.23</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="T19" s="3">
         <v>9.81</v>
       </c>
-      <c r="R19" s="3">
+      <c r="U19" s="3">
         <v>8.31</v>
       </c>
-      <c r="S19" s="3">
+      <c r="V19" s="3">
         <v>7.25</v>
       </c>
-      <c r="T19" s="3">
+      <c r="W19" s="3">
         <v>6.42</v>
       </c>
-      <c r="U19" s="3">
+      <c r="X19" s="3">
         <v>5.85</v>
       </c>
-      <c r="V19" s="3">
+      <c r="Y19" s="3">
         <v>5.58</v>
       </c>
-      <c r="W19" s="3">
+      <c r="Z19" s="3">
         <v>5.58</v>
       </c>
-      <c r="X19" s="3">
+      <c r="AA19" s="3">
         <v>5.71</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="AB19" s="3">
         <v>5.59</v>
       </c>
-      <c r="Z19" s="3">
+      <c r="AC19" s="3">
         <v>5.88</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="6">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="6">
         <v>24.5</v>
       </c>
-      <c r="F20" s="6">
+      <c r="I20" s="6">
         <v>27.4</v>
       </c>
-      <c r="G20" s="6">
+      <c r="J20" s="6">
         <v>23.1</v>
       </c>
-      <c r="H20" s="6">
+      <c r="K20" s="6">
         <v>23.1</v>
       </c>
-      <c r="I20" s="6">
+      <c r="L20" s="6">
         <v>21.7</v>
       </c>
-      <c r="J20" s="6">
+      <c r="M20" s="6">
         <v>22.1</v>
       </c>
-      <c r="K20" s="6">
+      <c r="N20" s="6">
         <v>23.9</v>
       </c>
-      <c r="L20" s="6">
+      <c r="O20" s="6">
         <v>19</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>24.58</v>
       </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
         <v>21.28</v>
       </c>
-      <c r="O20" s="3">
+      <c r="R20" s="3">
         <v>17.75</v>
       </c>
-      <c r="P20" s="3">
+      <c r="S20" s="3">
         <v>14.76</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>13.09</v>
       </c>
-      <c r="R20" s="3">
+      <c r="U20" s="3">
         <v>10.59</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>9.08</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>7.79</v>
       </c>
-      <c r="U20" s="3">
+      <c r="X20" s="3">
         <v>6.59</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Y20" s="3">
         <v>6.13</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Z20" s="3">
         <v>5.0599999999999996</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AA20" s="3">
         <v>4.7699999999999996</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AB20" s="3">
         <v>4.62</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AC20" s="3">
         <v>4.46</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="11">
         <v>14.8</v>
       </c>
-      <c r="C21" s="11">
+      <c r="F21" s="11">
         <v>13.7</v>
       </c>
-      <c r="D21" s="11">
+      <c r="G21" s="11">
         <v>14</v>
       </c>
-      <c r="E21" s="11">
+      <c r="H21" s="11">
         <v>13.5</v>
       </c>
-      <c r="F21" s="11">
+      <c r="I21" s="11">
         <v>14.1</v>
       </c>
-      <c r="G21" s="11">
+      <c r="J21" s="11">
         <v>12.6</v>
       </c>
-      <c r="H21" s="11">
+      <c r="K21" s="11">
         <v>11.9</v>
       </c>
-      <c r="I21" s="11">
+      <c r="L21" s="11">
         <v>11.5</v>
       </c>
-      <c r="J21" s="11">
+      <c r="M21" s="11">
         <v>11.1</v>
       </c>
-      <c r="K21" s="11">
+      <c r="N21" s="11">
         <v>10.3</v>
       </c>
-      <c r="L21" s="11">
+      <c r="O21" s="11">
         <v>9.1</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>10.53</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>10.01</v>
       </c>
-      <c r="O21" s="3">
+      <c r="R21" s="3">
         <v>9.7100000000000009</v>
       </c>
-      <c r="P21" s="3">
+      <c r="S21" s="3">
         <v>9.68</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="T21" s="3">
         <v>9.7899999999999991</v>
       </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <v>9.9</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
         <v>9.77</v>
       </c>
-      <c r="T21" s="3">
+      <c r="W21" s="3">
         <v>9.84</v>
       </c>
-      <c r="U21" s="3">
+      <c r="X21" s="3">
         <v>9.7899999999999991</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Y21" s="3">
         <v>9.6999999999999993</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Z21" s="3">
         <v>9.51</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AA21" s="3">
         <v>9.33</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AB21" s="3">
         <v>9.4700000000000006</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AC21" s="3">
         <v>9.57</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="11">
+        <v>25</v>
+      </c>
+      <c r="C22" s="11">
+        <v>24.2</v>
+      </c>
+      <c r="D22" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="E22" s="11">
+        <v>21.8</v>
+      </c>
+      <c r="F22" s="11">
+        <v>20</v>
+      </c>
+      <c r="G22" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="H22" s="11">
+        <v>15.6</v>
+      </c>
+      <c r="I22" s="11">
+        <v>16</v>
+      </c>
+      <c r="J22" s="11">
+        <v>13.8</v>
+      </c>
+      <c r="K22" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="L22" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="M22" s="11">
+        <v>12</v>
+      </c>
+      <c r="N22" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="O22" s="11">
+        <v>9.6</v>
+      </c>
+      <c r="P22" s="3">
+        <v>9.24</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>8.77</v>
+      </c>
+      <c r="R22" s="3">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="S22" s="3">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="T22" s="3">
+        <v>9.27</v>
+      </c>
+      <c r="U22" s="3">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="V22" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="W22" s="3">
+        <v>8.06</v>
+      </c>
+      <c r="X22" s="3">
+        <v>7.66</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>7.54</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>7.57</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>7.55</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>7.62</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
+++ b/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C358C0-E810-49C1-932C-4B0FD7BB8FE7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E7431D-57E1-4F81-B301-DAA42A45337D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="540" windowWidth="18960" windowHeight="23040" activeTab="2" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
+    <workbookView xWindow="8775" yWindow="300" windowWidth="21885" windowHeight="23040" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="3" r:id="rId1"/>
@@ -360,9 +360,6 @@
     <t xml:space="preserve">Ana M. Rothman, "Evolution of Fertility in Argentina and Uruguay", International Population Conference. London. 1969, vol. I, </t>
   </si>
   <si>
-    <t>тж. Finch, "A Political Economy of Uruguay since 1870", University of Liverpool, 1871, стр. 24.</t>
-  </si>
-  <si>
     <t>(International Union for the Scientific Study of the Population, Liege, 1971) vol. 1, стр. 716</t>
   </si>
   <si>
@@ -385,6 +382,9 @@
   </si>
   <si>
     <t>1890-94</t>
+  </si>
+  <si>
+    <t>тж. M. H. J. Finch, "A Political Economy of Uruguay since 1870", University of Liverpool, Macmillan, 1981, стр. 24.</t>
   </si>
 </sst>
 </file>
@@ -819,7 +819,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -829,22 +829,22 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1678,13 +1678,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>30</v>
@@ -3154,7 +3154,7 @@
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B22" s="16">
         <v>48.1</v>
@@ -3377,13 +3377,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>30</v>
@@ -4849,7 +4849,7 @@
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B22" s="11">
         <v>25</v>

--- a/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
+++ b/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E7431D-57E1-4F81-B301-DAA42A45337D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D089DF-FD06-4D2C-BC92-C3CB2D0F9F11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8775" yWindow="300" windowWidth="21885" windowHeight="23040" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="3" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="TFR (UN)" sheetId="9" r:id="rId8"/>
     <sheet name="NRR(UN)" sheetId="10" r:id="rId9"/>
     <sheet name="Population (UN)" sheetId="8" r:id="rId10"/>
+    <sheet name="Бриньоли" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="160">
   <si>
     <t>страна</t>
   </si>
@@ -385,6 +386,141 @@
   </si>
   <si>
     <t>тж. M. H. J. Finch, "A Political Economy of Uruguay since 1870", University of Liverpool, Macmillan, 1981, стр. 24.</t>
+  </si>
+  <si>
+    <t>Бриньоли</t>
+  </si>
+  <si>
+    <t>Реконструкция П. Бриньоли для ряда латиноамериканских стран</t>
+  </si>
+  <si>
+    <t>год</t>
+  </si>
+  <si>
+    <t>чн</t>
+  </si>
+  <si>
+    <t>мигр</t>
+  </si>
+  <si>
+    <t>р</t>
+  </si>
+  <si>
+    <t>с</t>
+  </si>
+  <si>
+    <t>еп</t>
+  </si>
+  <si>
+    <t>опж</t>
+  </si>
+  <si>
+    <t>бкв</t>
+  </si>
+  <si>
+    <t>чкв</t>
+  </si>
+  <si>
+    <t>мс</t>
+  </si>
+  <si>
+    <t>Венецуэлла</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>Población total</t>
+  </si>
+  <si>
+    <t>TMN</t>
+  </si>
+  <si>
+    <t>Tasa de migración neta</t>
+  </si>
+  <si>
+    <t>коэффициент чистой миграции, на 1000 населения</t>
+  </si>
+  <si>
+    <t>TBN</t>
+  </si>
+  <si>
+    <t>Tasa bruta de natalidad</t>
+  </si>
+  <si>
+    <t>общий / грубый коэффициент рождаемости, на 1000 населения</t>
+  </si>
+  <si>
+    <t>TBM</t>
+  </si>
+  <si>
+    <t>Tasa bruta de mortalidad</t>
+  </si>
+  <si>
+    <t>общий / грубый коэффициент смертности, на 1000 населения</t>
+  </si>
+  <si>
+    <t>TCN</t>
+  </si>
+  <si>
+    <t>Tasa de crecimiento natural</t>
+  </si>
+  <si>
+    <t>коэффициент естественного прироста, на 1000; фактически TBN − TBM</t>
+  </si>
+  <si>
+    <t>e0</t>
+  </si>
+  <si>
+    <t>Esperanza de vida al nacimiento</t>
+  </si>
+  <si>
+    <t>ожидаемая продолжительность жизни при рождении, в годах</t>
+  </si>
+  <si>
+    <t>TBR</t>
+  </si>
+  <si>
+    <t>Tasa bruta de reproducción</t>
+  </si>
+  <si>
+    <t>TNR</t>
+  </si>
+  <si>
+    <t>Tasa neta de reproducción</t>
+  </si>
+  <si>
+    <t>q0</t>
+  </si>
+  <si>
+    <t>Tasa de mortalidad infantil</t>
+  </si>
+  <si>
+    <t>Исправленные опечатки помечены синим фоном</t>
+  </si>
+  <si>
+    <t>Реконструкция П. Бриньоли (1993) для ряда латиноамериканских стран</t>
+  </si>
+  <si>
+    <t>общая численность населения, в тыс. чел.</t>
+  </si>
+  <si>
+    <t>Héctor Pérez Brignoli, "América Latina en la transición demográfica, 1800-1980"</t>
+  </si>
+  <si>
+    <t>перепечатка в Población y Salud en Mesoamérica, Vol. 7, Núm. 2, enero-junio, 2010, pp. 1-29</t>
+  </si>
+  <si>
+    <t>первоначально в IV Conferencia Latinoamericana de Población, Ciudad de México, 23 al 26 de marzo (1993)</t>
+  </si>
+  <si>
+    <t>младенческая смертность как вероятность умереть до 1 года, на 1000 живых рождений</t>
+  </si>
+  <si>
+    <t>нетто-коэффициент воспроизводства: среднее число дочерей на женщину с учётом женской смертности до и в репродуктивных возрастах.</t>
+  </si>
+  <si>
+    <t>брутто-коэффициент воспроизводства: среднее число дочерей на женщину при данной рождаемости, без учёта смертности женщин до и в репродуктивных возрастах</t>
   </si>
 </sst>
 </file>
@@ -395,7 +531,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,6 +549,28 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -450,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -470,6 +628,27 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,8 +963,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C2E48C-64F2-4716-9126-743AC29B124D}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -872,6 +1054,14 @@
         <v>87</v>
       </c>
     </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="3"/>
@@ -880,25 +1070,33 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
@@ -931,12 +1129,6 @@
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1642,6 +1834,5291 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9BC21F-474B-49BD-9F91-A9A4D85B1EA9}">
+  <dimension ref="A1:O181"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L17" s="18"/>
+      <c r="M17" s="10"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>1752</v>
+      </c>
+      <c r="B18" s="4">
+        <v>25.3</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="23">
+        <v>37.9</v>
+      </c>
+      <c r="E18" s="23">
+        <v>33</v>
+      </c>
+      <c r="F18" s="23">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G18" s="23">
+        <v>30.1</v>
+      </c>
+      <c r="H18" s="23">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="I18" s="23">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="J18" s="19">
+        <v>323</v>
+      </c>
+      <c r="L18" s="12"/>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>1757</v>
+      </c>
+      <c r="B19" s="4">
+        <v>25.93</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="23">
+        <v>37.9</v>
+      </c>
+      <c r="E19" s="23">
+        <v>33</v>
+      </c>
+      <c r="F19" s="23">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G19" s="23">
+        <v>30.2</v>
+      </c>
+      <c r="H19" s="23">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="I19" s="23">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J19" s="19">
+        <v>322</v>
+      </c>
+      <c r="L19" s="12"/>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>1762</v>
+      </c>
+      <c r="B20" s="4">
+        <v>26.58</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="23">
+        <v>37.9</v>
+      </c>
+      <c r="E20" s="23">
+        <v>32.9</v>
+      </c>
+      <c r="F20" s="23">
+        <v>5</v>
+      </c>
+      <c r="G20" s="23">
+        <v>30.4</v>
+      </c>
+      <c r="H20" s="23">
+        <v>2.46</v>
+      </c>
+      <c r="I20" s="23">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J20" s="19">
+        <v>321</v>
+      </c>
+      <c r="L20" s="12"/>
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>1767</v>
+      </c>
+      <c r="B21" s="4">
+        <v>27.26</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="23">
+        <v>37.9</v>
+      </c>
+      <c r="E21" s="23">
+        <v>32.9</v>
+      </c>
+      <c r="F21" s="23">
+        <v>5</v>
+      </c>
+      <c r="G21" s="23">
+        <v>30.4</v>
+      </c>
+      <c r="H21" s="23">
+        <v>2.46</v>
+      </c>
+      <c r="I21" s="23">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J21" s="19">
+        <v>320</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>1772</v>
+      </c>
+      <c r="B22" s="4">
+        <v>28.41</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="23">
+        <v>38.6</v>
+      </c>
+      <c r="E22" s="23">
+        <v>27.2</v>
+      </c>
+      <c r="F22" s="23">
+        <v>11.4</v>
+      </c>
+      <c r="G22" s="23">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="H22" s="23">
+        <v>2.54</v>
+      </c>
+      <c r="I22" s="23">
+        <v>1.37</v>
+      </c>
+      <c r="J22" s="19">
+        <v>260</v>
+      </c>
+      <c r="L22" s="12"/>
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>1777</v>
+      </c>
+      <c r="B23" s="4">
+        <v>30.99</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+      <c r="D23" s="23">
+        <v>46.7</v>
+      </c>
+      <c r="E23" s="23">
+        <v>23.4</v>
+      </c>
+      <c r="F23" s="23">
+        <v>23.4</v>
+      </c>
+      <c r="G23" s="23">
+        <v>43.7</v>
+      </c>
+      <c r="H23" s="23">
+        <v>3.22</v>
+      </c>
+      <c r="I23" s="23">
+        <v>2.04</v>
+      </c>
+      <c r="J23" s="19">
+        <v>205</v>
+      </c>
+      <c r="L23" s="12"/>
+      <c r="M23" s="4"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
+        <v>1782</v>
+      </c>
+      <c r="B24" s="4">
+        <v>32.69</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D24" s="23">
+        <v>45.6</v>
+      </c>
+      <c r="E24" s="23">
+        <v>47.7</v>
+      </c>
+      <c r="F24" s="23">
+        <v>-2.1</v>
+      </c>
+      <c r="G24" s="23">
+        <v>21.4</v>
+      </c>
+      <c r="H24" s="23">
+        <v>3.24</v>
+      </c>
+      <c r="I24" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="J24" s="19">
+        <v>427</v>
+      </c>
+      <c r="L24" s="12"/>
+      <c r="M24" s="4"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>1787</v>
+      </c>
+      <c r="B25" s="4">
+        <v>34.86</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D25" s="23">
+        <v>52</v>
+      </c>
+      <c r="E25" s="23">
+        <v>24.2</v>
+      </c>
+      <c r="F25" s="23">
+        <v>27.7</v>
+      </c>
+      <c r="G25" s="23">
+        <v>43</v>
+      </c>
+      <c r="H25" s="23">
+        <v>3.79</v>
+      </c>
+      <c r="I25" s="23">
+        <v>2.36</v>
+      </c>
+      <c r="J25" s="19">
+        <v>210</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="4"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>1792</v>
+      </c>
+      <c r="B26" s="4">
+        <v>39.979999999999997</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D26" s="23">
+        <v>50.6</v>
+      </c>
+      <c r="E26" s="23">
+        <v>23.7</v>
+      </c>
+      <c r="F26" s="23">
+        <v>26.9</v>
+      </c>
+      <c r="G26" s="23">
+        <v>43.5</v>
+      </c>
+      <c r="H26" s="23">
+        <v>3.85</v>
+      </c>
+      <c r="I26" s="23">
+        <v>2.42</v>
+      </c>
+      <c r="J26" s="19">
+        <v>207</v>
+      </c>
+      <c r="L26" s="12"/>
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>1797</v>
+      </c>
+      <c r="B27" s="4">
+        <v>45.55</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="23">
+        <v>48.9</v>
+      </c>
+      <c r="E27" s="23">
+        <v>23.9</v>
+      </c>
+      <c r="F27" s="23">
+        <v>25.1</v>
+      </c>
+      <c r="G27" s="23">
+        <v>42.4</v>
+      </c>
+      <c r="H27" s="23">
+        <v>3.79</v>
+      </c>
+      <c r="I27" s="23">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="J27" s="19">
+        <v>215</v>
+      </c>
+      <c r="L27" s="12"/>
+      <c r="M27" s="4"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>1802</v>
+      </c>
+      <c r="B28" s="4">
+        <v>50.47</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="23">
+        <v>49.1</v>
+      </c>
+      <c r="E28" s="23">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F28" s="23">
+        <v>15.8</v>
+      </c>
+      <c r="G28" s="23">
+        <v>31.9</v>
+      </c>
+      <c r="H28" s="23">
+        <v>3.73</v>
+      </c>
+      <c r="I28" s="23">
+        <v>1.75</v>
+      </c>
+      <c r="J28" s="19">
+        <v>305</v>
+      </c>
+      <c r="L28" s="12"/>
+      <c r="M28" s="4"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>1807</v>
+      </c>
+      <c r="B29" s="4">
+        <v>53.97</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="23">
+        <v>44</v>
+      </c>
+      <c r="E29" s="23">
+        <v>33.1</v>
+      </c>
+      <c r="F29" s="23">
+        <v>10.9</v>
+      </c>
+      <c r="G29" s="23">
+        <v>30.2</v>
+      </c>
+      <c r="H29" s="23">
+        <v>3.1</v>
+      </c>
+      <c r="I29" s="23">
+        <v>1.38</v>
+      </c>
+      <c r="J29" s="19">
+        <v>323</v>
+      </c>
+      <c r="L29" s="12"/>
+      <c r="M29" s="4"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
+        <v>1812</v>
+      </c>
+      <c r="B30" s="4">
+        <v>58.57</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D30" s="23">
+        <v>47.2</v>
+      </c>
+      <c r="E30" s="23">
+        <v>25.7</v>
+      </c>
+      <c r="F30" s="23">
+        <v>21.6</v>
+      </c>
+      <c r="G30" s="23">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="H30" s="23">
+        <v>3.05</v>
+      </c>
+      <c r="I30" s="23">
+        <v>1.71</v>
+      </c>
+      <c r="J30" s="19">
+        <v>247</v>
+      </c>
+      <c r="L30" s="12"/>
+      <c r="M30" s="4"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>1817</v>
+      </c>
+      <c r="B31" s="4">
+        <v>65.55</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D31" s="23">
+        <v>47.6</v>
+      </c>
+      <c r="E31" s="23">
+        <v>24.4</v>
+      </c>
+      <c r="F31" s="23">
+        <v>23.3</v>
+      </c>
+      <c r="G31" s="23">
+        <v>40.1</v>
+      </c>
+      <c r="H31" s="23">
+        <v>2.96</v>
+      </c>
+      <c r="I31" s="23">
+        <v>1.73</v>
+      </c>
+      <c r="J31" s="19">
+        <v>233</v>
+      </c>
+      <c r="L31" s="12"/>
+      <c r="M31" s="4"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>1822</v>
+      </c>
+      <c r="B32" s="4">
+        <v>72.52</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D32" s="23">
+        <v>45.7</v>
+      </c>
+      <c r="E32" s="23">
+        <v>28.8</v>
+      </c>
+      <c r="F32" s="23">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="G32" s="23">
+        <v>34.6</v>
+      </c>
+      <c r="H32" s="23">
+        <v>2.86</v>
+      </c>
+      <c r="I32" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="J32" s="19">
+        <v>280</v>
+      </c>
+      <c r="L32" s="12"/>
+      <c r="M32" s="4"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
+        <v>1827</v>
+      </c>
+      <c r="B33" s="4">
+        <v>79.150000000000006</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="23">
+        <v>42.4</v>
+      </c>
+      <c r="E33" s="23">
+        <v>24.5</v>
+      </c>
+      <c r="F33" s="23">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="G33" s="23">
+        <v>38.1</v>
+      </c>
+      <c r="H33" s="23">
+        <v>2.72</v>
+      </c>
+      <c r="I33" s="23">
+        <v>1.51</v>
+      </c>
+      <c r="J33" s="19">
+        <v>249</v>
+      </c>
+      <c r="L33" s="12"/>
+      <c r="M33" s="4"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
+        <v>1832</v>
+      </c>
+      <c r="B34" s="4">
+        <v>86.34</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D34" s="23">
+        <v>42.4</v>
+      </c>
+      <c r="E34" s="23">
+        <v>25.8</v>
+      </c>
+      <c r="F34" s="23">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G34" s="23">
+        <v>36.5</v>
+      </c>
+      <c r="H34" s="23">
+        <v>2.77</v>
+      </c>
+      <c r="I34" s="23">
+        <v>1.48</v>
+      </c>
+      <c r="J34" s="19">
+        <v>263</v>
+      </c>
+      <c r="L34" s="12"/>
+      <c r="M34" s="4"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
+        <v>1837</v>
+      </c>
+      <c r="B35" s="4">
+        <v>94.72</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D35" s="23">
+        <v>40.6</v>
+      </c>
+      <c r="E35" s="23">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F35" s="23">
+        <v>20.2</v>
+      </c>
+      <c r="G35" s="23">
+        <v>43</v>
+      </c>
+      <c r="H35" s="23">
+        <v>2.65</v>
+      </c>
+      <c r="I35" s="23">
+        <v>1.65</v>
+      </c>
+      <c r="J35" s="19">
+        <v>211</v>
+      </c>
+      <c r="L35" s="12"/>
+      <c r="M35" s="4"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
+        <v>1842</v>
+      </c>
+      <c r="B36" s="4">
+        <v>104.89</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D36" s="23">
+        <v>40.5</v>
+      </c>
+      <c r="E36" s="23">
+        <v>20.2</v>
+      </c>
+      <c r="F36" s="23">
+        <v>20.3</v>
+      </c>
+      <c r="G36" s="23">
+        <v>43.5</v>
+      </c>
+      <c r="H36" s="23">
+        <v>2.63</v>
+      </c>
+      <c r="I36" s="23">
+        <v>1.65</v>
+      </c>
+      <c r="J36" s="19">
+        <v>207</v>
+      </c>
+      <c r="L36" s="12"/>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="19">
+        <v>1847</v>
+      </c>
+      <c r="B37" s="4">
+        <v>116.61</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D37" s="23">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="E37" s="23">
+        <v>18.5</v>
+      </c>
+      <c r="F37" s="23">
+        <v>21.8</v>
+      </c>
+      <c r="G37" s="23">
+        <v>46.1</v>
+      </c>
+      <c r="H37" s="23">
+        <v>2.65</v>
+      </c>
+      <c r="I37" s="23">
+        <v>1.76</v>
+      </c>
+      <c r="J37" s="19">
+        <v>188</v>
+      </c>
+      <c r="L37" s="12"/>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="19">
+        <v>1852</v>
+      </c>
+      <c r="B38" s="4">
+        <v>127.63</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D38" s="23">
+        <v>40.9</v>
+      </c>
+      <c r="E38" s="23">
+        <v>26.9</v>
+      </c>
+      <c r="F38" s="23">
+        <v>14</v>
+      </c>
+      <c r="G38" s="23">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="H38" s="23">
+        <v>2.72</v>
+      </c>
+      <c r="I38" s="23">
+        <v>1.42</v>
+      </c>
+      <c r="J38" s="19">
+        <v>270</v>
+      </c>
+      <c r="L38" s="12"/>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="19">
+        <v>1857</v>
+      </c>
+      <c r="B39" s="4">
+        <v>133.84</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D39" s="23">
+        <v>41.6</v>
+      </c>
+      <c r="E39" s="23">
+        <v>37</v>
+      </c>
+      <c r="F39" s="23">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G39" s="23">
+        <v>26.1</v>
+      </c>
+      <c r="H39" s="23">
+        <v>2.72</v>
+      </c>
+      <c r="I39" s="23">
+        <v>1.04</v>
+      </c>
+      <c r="J39" s="19">
+        <v>368</v>
+      </c>
+      <c r="L39" s="12"/>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
+        <v>1862</v>
+      </c>
+      <c r="B40" s="4">
+        <v>141.58000000000001</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D40" s="23">
+        <v>44.4</v>
+      </c>
+      <c r="E40" s="23">
+        <v>26.9</v>
+      </c>
+      <c r="F40" s="23">
+        <v>17.5</v>
+      </c>
+      <c r="G40" s="23">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="H40" s="23">
+        <v>2.83</v>
+      </c>
+      <c r="I40" s="23">
+        <v>1.52</v>
+      </c>
+      <c r="J40" s="19">
+        <v>261</v>
+      </c>
+      <c r="L40" s="12"/>
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="19">
+        <v>1867</v>
+      </c>
+      <c r="B41" s="4">
+        <v>154.83000000000001</v>
+      </c>
+      <c r="C41" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D41" s="23">
+        <v>46</v>
+      </c>
+      <c r="E41" s="23">
+        <v>28.1</v>
+      </c>
+      <c r="F41" s="23">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="G41" s="23">
+        <v>36.4</v>
+      </c>
+      <c r="H41" s="23">
+        <v>2.95</v>
+      </c>
+      <c r="I41" s="23">
+        <v>1.57</v>
+      </c>
+      <c r="J41" s="19">
+        <v>264</v>
+      </c>
+      <c r="L41" s="12"/>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
+        <v>1872</v>
+      </c>
+      <c r="B42" s="4">
+        <v>170.14</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D42" s="23">
+        <v>46.3</v>
+      </c>
+      <c r="E42" s="23">
+        <v>26.9</v>
+      </c>
+      <c r="F42" s="23">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="G42" s="23">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="H42" s="23">
+        <v>3.07</v>
+      </c>
+      <c r="I42" s="23">
+        <v>1.69</v>
+      </c>
+      <c r="J42" s="19">
+        <v>253</v>
+      </c>
+      <c r="L42" s="12"/>
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
+        <v>1877</v>
+      </c>
+      <c r="B43" s="4">
+        <v>188.08</v>
+      </c>
+      <c r="C43" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D43" s="23">
+        <v>45.1</v>
+      </c>
+      <c r="E43" s="23">
+        <v>24.9</v>
+      </c>
+      <c r="F43" s="23">
+        <v>20.3</v>
+      </c>
+      <c r="G43" s="23">
+        <v>39.6</v>
+      </c>
+      <c r="H43" s="23">
+        <v>3.15</v>
+      </c>
+      <c r="I43" s="23">
+        <v>1.82</v>
+      </c>
+      <c r="J43" s="19">
+        <v>237</v>
+      </c>
+      <c r="L43" s="12"/>
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
+        <v>1882</v>
+      </c>
+      <c r="B44" s="4">
+        <v>207.72</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D44" s="23">
+        <v>41.6</v>
+      </c>
+      <c r="E44" s="23">
+        <v>22.6</v>
+      </c>
+      <c r="F44" s="23">
+        <v>19</v>
+      </c>
+      <c r="G44" s="23">
+        <v>41.4</v>
+      </c>
+      <c r="H44" s="23">
+        <v>2.99</v>
+      </c>
+      <c r="I44" s="23">
+        <v>1.79</v>
+      </c>
+      <c r="J44" s="19">
+        <v>223</v>
+      </c>
+      <c r="L44" s="12"/>
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
+        <v>1887</v>
+      </c>
+      <c r="B45" s="4">
+        <v>228.82</v>
+      </c>
+      <c r="C45" s="3">
+        <v>0</v>
+      </c>
+      <c r="D45" s="23">
+        <v>43.8</v>
+      </c>
+      <c r="E45" s="23">
+        <v>24.3</v>
+      </c>
+      <c r="F45" s="23">
+        <v>19.5</v>
+      </c>
+      <c r="G45" s="23">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="H45" s="23">
+        <v>3.11</v>
+      </c>
+      <c r="I45" s="23">
+        <v>1.8</v>
+      </c>
+      <c r="J45" s="19">
+        <v>236</v>
+      </c>
+      <c r="L45" s="12"/>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="19">
+        <v>1892</v>
+      </c>
+      <c r="B46" s="4">
+        <v>251.58</v>
+      </c>
+      <c r="C46" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="D46" s="23">
+        <v>45.1</v>
+      </c>
+      <c r="E46" s="23">
+        <v>30.6</v>
+      </c>
+      <c r="F46" s="23">
+        <v>14.5</v>
+      </c>
+      <c r="G46" s="23">
+        <v>33.1</v>
+      </c>
+      <c r="H46" s="23">
+        <v>3.05</v>
+      </c>
+      <c r="I46" s="23">
+        <v>1.48</v>
+      </c>
+      <c r="J46" s="19">
+        <v>294</v>
+      </c>
+      <c r="L46" s="12"/>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="19">
+        <v>1897</v>
+      </c>
+      <c r="B47" s="4">
+        <v>275.66000000000003</v>
+      </c>
+      <c r="C47" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="D47" s="23">
+        <v>45.5</v>
+      </c>
+      <c r="E47" s="23">
+        <v>31.9</v>
+      </c>
+      <c r="F47" s="23">
+        <v>13.6</v>
+      </c>
+      <c r="G47" s="23">
+        <v>31.9</v>
+      </c>
+      <c r="H47" s="23">
+        <v>2.87</v>
+      </c>
+      <c r="I47" s="23">
+        <v>1.35</v>
+      </c>
+      <c r="J47" s="19">
+        <v>306</v>
+      </c>
+      <c r="L47" s="12"/>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="19">
+        <v>1902</v>
+      </c>
+      <c r="B48" s="4">
+        <v>302.01</v>
+      </c>
+      <c r="C48" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="D48" s="23">
+        <v>43.1</v>
+      </c>
+      <c r="E48" s="23">
+        <v>30</v>
+      </c>
+      <c r="F48" s="23">
+        <v>13.1</v>
+      </c>
+      <c r="G48" s="23">
+        <v>33</v>
+      </c>
+      <c r="H48" s="23">
+        <v>2.62</v>
+      </c>
+      <c r="I48" s="23">
+        <v>1.27</v>
+      </c>
+      <c r="J48" s="19">
+        <v>295</v>
+      </c>
+      <c r="L48" s="12"/>
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="19">
+        <v>1907</v>
+      </c>
+      <c r="B49" s="4">
+        <v>332.63</v>
+      </c>
+      <c r="C49" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="D49" s="23">
+        <v>47.3</v>
+      </c>
+      <c r="E49" s="23">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="F49" s="23">
+        <v>15.1</v>
+      </c>
+      <c r="G49" s="23">
+        <v>31.9</v>
+      </c>
+      <c r="H49" s="23">
+        <v>2.86</v>
+      </c>
+      <c r="I49" s="23">
+        <v>1.34</v>
+      </c>
+      <c r="J49" s="19">
+        <v>305</v>
+      </c>
+      <c r="L49" s="12"/>
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="19">
+        <v>1912</v>
+      </c>
+      <c r="B50" s="4">
+        <v>372.57</v>
+      </c>
+      <c r="C50" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="D50" s="23">
+        <v>50.8</v>
+      </c>
+      <c r="E50" s="23">
+        <v>30.5</v>
+      </c>
+      <c r="F50" s="23">
+        <v>20.3</v>
+      </c>
+      <c r="G50" s="23">
+        <v>34.6</v>
+      </c>
+      <c r="H50" s="23">
+        <v>3.17</v>
+      </c>
+      <c r="I50" s="23">
+        <v>1.61</v>
+      </c>
+      <c r="J50" s="19">
+        <v>280</v>
+      </c>
+      <c r="L50" s="12"/>
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="19">
+        <v>1917</v>
+      </c>
+      <c r="B51" s="4">
+        <v>411.79</v>
+      </c>
+      <c r="C51" s="3">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="D51" s="23">
+        <v>48.6</v>
+      </c>
+      <c r="E51" s="23">
+        <v>32.5</v>
+      </c>
+      <c r="F51" s="23">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="G51" s="23">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="H51" s="23">
+        <v>3.22</v>
+      </c>
+      <c r="I51" s="23">
+        <v>1.53</v>
+      </c>
+      <c r="J51" s="19">
+        <v>302</v>
+      </c>
+      <c r="L51" s="12"/>
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="19">
+        <v>1922</v>
+      </c>
+      <c r="B52" s="4">
+        <v>446.82</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="D52" s="23">
+        <v>46</v>
+      </c>
+      <c r="E52" s="23">
+        <v>29.5</v>
+      </c>
+      <c r="F52" s="23">
+        <v>16.5</v>
+      </c>
+      <c r="G52" s="23">
+        <v>34.1</v>
+      </c>
+      <c r="H52" s="23">
+        <v>3.24</v>
+      </c>
+      <c r="I52" s="23">
+        <v>1.62</v>
+      </c>
+      <c r="J52" s="19">
+        <v>285</v>
+      </c>
+      <c r="L52" s="12"/>
+      <c r="M52" s="4"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="19">
+        <v>1927</v>
+      </c>
+      <c r="B53" s="4">
+        <v>494.12</v>
+      </c>
+      <c r="C53" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D53" s="23">
+        <v>48.8</v>
+      </c>
+      <c r="E53" s="23">
+        <v>27.7</v>
+      </c>
+      <c r="F53" s="23">
+        <v>21.2</v>
+      </c>
+      <c r="G53" s="23">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="H53" s="23">
+        <v>3.48</v>
+      </c>
+      <c r="I53" s="23">
+        <v>1.87</v>
+      </c>
+      <c r="J53" s="19">
+        <v>260</v>
+      </c>
+      <c r="L53" s="12"/>
+      <c r="M53" s="4"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="19">
+        <v>1932</v>
+      </c>
+      <c r="B54" s="4">
+        <v>553.05999999999995</v>
+      </c>
+      <c r="C54" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D54" s="23">
+        <v>46.9</v>
+      </c>
+      <c r="E54" s="23">
+        <v>24.7</v>
+      </c>
+      <c r="F54" s="23">
+        <v>22.3</v>
+      </c>
+      <c r="G54" s="23">
+        <v>39.9</v>
+      </c>
+      <c r="H54" s="23">
+        <v>3.34</v>
+      </c>
+      <c r="I54" s="23">
+        <v>1.94</v>
+      </c>
+      <c r="J54" s="19">
+        <v>234</v>
+      </c>
+      <c r="L54" s="12"/>
+      <c r="M54" s="4"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="19">
+        <v>1937</v>
+      </c>
+      <c r="B55" s="4">
+        <v>620.99</v>
+      </c>
+      <c r="C55" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D55" s="23">
+        <v>45.7</v>
+      </c>
+      <c r="E55" s="23">
+        <v>22.5</v>
+      </c>
+      <c r="F55" s="23">
+        <v>23.3</v>
+      </c>
+      <c r="G55" s="23">
+        <v>42.4</v>
+      </c>
+      <c r="H55" s="23">
+        <v>3.23</v>
+      </c>
+      <c r="I55" s="23">
+        <v>1.98</v>
+      </c>
+      <c r="J55" s="19">
+        <v>216</v>
+      </c>
+      <c r="L55" s="12"/>
+      <c r="M55" s="4"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="19">
+        <v>1942</v>
+      </c>
+      <c r="B56" s="4">
+        <v>700.31</v>
+      </c>
+      <c r="C56" s="3">
+        <v>0</v>
+      </c>
+      <c r="D56" s="23">
+        <v>44.6</v>
+      </c>
+      <c r="E56" s="23">
+        <v>20.2</v>
+      </c>
+      <c r="F56" s="23">
+        <v>24.5</v>
+      </c>
+      <c r="G56" s="23">
+        <v>45.1</v>
+      </c>
+      <c r="H56" s="23">
+        <v>3.15</v>
+      </c>
+      <c r="I56" s="23">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="J56" s="19">
+        <v>195</v>
+      </c>
+      <c r="L56" s="12"/>
+      <c r="M56" s="4"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="19">
+        <v>1947</v>
+      </c>
+      <c r="B57" s="4">
+        <v>802.33</v>
+      </c>
+      <c r="C57" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D57" s="23">
+        <v>44.7</v>
+      </c>
+      <c r="E57" s="23">
+        <v>15.4</v>
+      </c>
+      <c r="F57" s="23">
+        <v>29.3</v>
+      </c>
+      <c r="G57" s="23">
+        <v>52.1</v>
+      </c>
+      <c r="H57" s="23">
+        <v>3.16</v>
+      </c>
+      <c r="I57" s="23">
+        <v>2.34</v>
+      </c>
+      <c r="J57" s="19">
+        <v>148</v>
+      </c>
+      <c r="L57" s="12"/>
+      <c r="M57" s="4"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="19">
+        <v>1952</v>
+      </c>
+      <c r="B58" s="4">
+        <v>942.68</v>
+      </c>
+      <c r="C58" s="3">
+        <v>0</v>
+      </c>
+      <c r="D58" s="23">
+        <v>47.1</v>
+      </c>
+      <c r="E58" s="23">
+        <v>12.6</v>
+      </c>
+      <c r="F58" s="23">
+        <v>34.5</v>
+      </c>
+      <c r="G58" s="23">
+        <v>57</v>
+      </c>
+      <c r="H58" s="23">
+        <v>3.36</v>
+      </c>
+      <c r="I58" s="23">
+        <v>2.69</v>
+      </c>
+      <c r="J58" s="19">
+        <v>199</v>
+      </c>
+      <c r="L58" s="12"/>
+      <c r="M58" s="4"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B59" s="5"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="19"/>
+      <c r="L59" s="12"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="23"/>
+      <c r="J60" s="19"/>
+      <c r="L60" s="12"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B61" s="5"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="19"/>
+      <c r="L61" s="12"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F62" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G62" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H62" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I62" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L62" s="12"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1872</v>
+      </c>
+      <c r="B63" s="5">
+        <v>1947</v>
+      </c>
+      <c r="C63" s="3">
+        <v>11</v>
+      </c>
+      <c r="D63" s="23">
+        <v>49</v>
+      </c>
+      <c r="E63" s="23">
+        <v>32</v>
+      </c>
+      <c r="F63" s="23">
+        <v>17</v>
+      </c>
+      <c r="G63" s="23">
+        <v>31.5</v>
+      </c>
+      <c r="H63" s="23">
+        <v>3.25</v>
+      </c>
+      <c r="I63" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="J63" s="19">
+        <v>284</v>
+      </c>
+      <c r="L63" s="12"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1877</v>
+      </c>
+      <c r="B64" s="5">
+        <v>2207</v>
+      </c>
+      <c r="C64" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D64" s="23">
+        <v>49</v>
+      </c>
+      <c r="E64" s="23">
+        <v>30</v>
+      </c>
+      <c r="F64" s="23">
+        <v>19</v>
+      </c>
+      <c r="G64" s="23">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="H64" s="23">
+        <v>3.14</v>
+      </c>
+      <c r="I64" s="23">
+        <v>1.53</v>
+      </c>
+      <c r="J64" s="19">
+        <v>267</v>
+      </c>
+      <c r="L64" s="12"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1882</v>
+      </c>
+      <c r="B65" s="5">
+        <v>2524</v>
+      </c>
+      <c r="C65" s="3">
+        <v>12.8</v>
+      </c>
+      <c r="D65" s="23">
+        <v>49</v>
+      </c>
+      <c r="E65" s="23">
+        <v>30</v>
+      </c>
+      <c r="F65" s="23">
+        <v>19</v>
+      </c>
+      <c r="G65" s="23">
+        <v>33.1</v>
+      </c>
+      <c r="H65" s="23">
+        <v>3.12</v>
+      </c>
+      <c r="I65" s="23">
+        <v>1.51</v>
+      </c>
+      <c r="J65" s="19">
+        <v>267</v>
+      </c>
+      <c r="L65" s="12"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1887</v>
+      </c>
+      <c r="B66" s="5">
+        <v>3125</v>
+      </c>
+      <c r="C66" s="3">
+        <v>44.1</v>
+      </c>
+      <c r="D66" s="23">
+        <v>46.4</v>
+      </c>
+      <c r="E66" s="23">
+        <v>30.2</v>
+      </c>
+      <c r="F66" s="23">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="G66" s="23">
+        <v>32.6</v>
+      </c>
+      <c r="H66" s="23">
+        <v>2.67</v>
+      </c>
+      <c r="I66" s="23">
+        <v>1.27</v>
+      </c>
+      <c r="J66" s="19">
+        <v>273</v>
+      </c>
+      <c r="L66" s="12"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1892</v>
+      </c>
+      <c r="B67" s="5">
+        <v>3795</v>
+      </c>
+      <c r="C67" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D67" s="23">
+        <v>44</v>
+      </c>
+      <c r="E67" s="23">
+        <v>29</v>
+      </c>
+      <c r="F67" s="23">
+        <v>15</v>
+      </c>
+      <c r="G67" s="23">
+        <v>34</v>
+      </c>
+      <c r="H67" s="23">
+        <v>2.37</v>
+      </c>
+      <c r="I67" s="23">
+        <v>1.18</v>
+      </c>
+      <c r="J67" s="19">
+        <v>260</v>
+      </c>
+      <c r="L67" s="12"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1897</v>
+      </c>
+      <c r="B68" s="5">
+        <v>4334</v>
+      </c>
+      <c r="C68" s="3">
+        <v>15</v>
+      </c>
+      <c r="D68" s="23">
+        <v>45.1</v>
+      </c>
+      <c r="E68" s="23">
+        <v>29</v>
+      </c>
+      <c r="F68" s="23">
+        <v>16</v>
+      </c>
+      <c r="G68" s="23">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="H68" s="23">
+        <v>2.69</v>
+      </c>
+      <c r="I68" s="23">
+        <v>1.31</v>
+      </c>
+      <c r="J68" s="19">
+        <v>266</v>
+      </c>
+      <c r="L68" s="12"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1902</v>
+      </c>
+      <c r="B69" s="5">
+        <v>5006</v>
+      </c>
+      <c r="C69" s="3">
+        <v>10.4</v>
+      </c>
+      <c r="D69" s="23">
+        <v>44</v>
+      </c>
+      <c r="E69" s="23">
+        <v>26</v>
+      </c>
+      <c r="F69" s="23">
+        <v>18</v>
+      </c>
+      <c r="G69" s="23">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="H69" s="23">
+        <v>2.73</v>
+      </c>
+      <c r="I69" s="23">
+        <v>1.47</v>
+      </c>
+      <c r="J69" s="19">
+        <v>234</v>
+      </c>
+      <c r="L69" s="12"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1907</v>
+      </c>
+      <c r="B70" s="5">
+        <v>6006</v>
+      </c>
+      <c r="C70" s="3">
+        <v>29.3</v>
+      </c>
+      <c r="D70" s="23">
+        <v>42.2</v>
+      </c>
+      <c r="E70" s="23">
+        <v>23.1</v>
+      </c>
+      <c r="F70" s="23">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="G70" s="23">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="H70" s="23">
+        <v>2.63</v>
+      </c>
+      <c r="I70" s="23">
+        <v>1.52</v>
+      </c>
+      <c r="J70" s="19">
+        <v>210</v>
+      </c>
+      <c r="L70" s="12"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1912</v>
+      </c>
+      <c r="B71" s="5">
+        <v>7410</v>
+      </c>
+      <c r="C71" s="3">
+        <v>21.9</v>
+      </c>
+      <c r="D71" s="23">
+        <v>39.1</v>
+      </c>
+      <c r="E71" s="23">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F71" s="23">
+        <v>19</v>
+      </c>
+      <c r="G71" s="23">
+        <v>43.5</v>
+      </c>
+      <c r="H71" s="23">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="I71" s="23">
+        <v>1.46</v>
+      </c>
+      <c r="J71" s="19">
+        <v>181</v>
+      </c>
+      <c r="L71" s="12"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1917</v>
+      </c>
+      <c r="B72" s="5">
+        <v>8529</v>
+      </c>
+      <c r="C72" s="3">
+        <v>-1.6</v>
+      </c>
+      <c r="D72" s="23">
+        <v>37</v>
+      </c>
+      <c r="E72" s="23">
+        <v>18</v>
+      </c>
+      <c r="F72" s="23">
+        <v>19</v>
+      </c>
+      <c r="G72" s="23">
+        <v>46.2</v>
+      </c>
+      <c r="H72" s="23">
+        <v>2.33</v>
+      </c>
+      <c r="I72" s="23">
+        <v>1.55</v>
+      </c>
+      <c r="J72" s="19">
+        <v>163</v>
+      </c>
+      <c r="L72" s="12"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1922</v>
+      </c>
+      <c r="B73" s="5">
+        <v>9612</v>
+      </c>
+      <c r="C73" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="D73" s="23">
+        <v>35</v>
+      </c>
+      <c r="E73" s="23">
+        <v>15</v>
+      </c>
+      <c r="F73" s="23">
+        <v>20</v>
+      </c>
+      <c r="G73" s="23">
+        <v>50.2</v>
+      </c>
+      <c r="H73" s="23">
+        <v>2.44</v>
+      </c>
+      <c r="I73" s="23">
+        <v>1.74</v>
+      </c>
+      <c r="J73" s="19">
+        <v>136</v>
+      </c>
+      <c r="L73" s="12"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1927</v>
+      </c>
+      <c r="B74" s="5">
+        <v>11114</v>
+      </c>
+      <c r="C74" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D74" s="23">
+        <v>33</v>
+      </c>
+      <c r="E74" s="23">
+        <v>14</v>
+      </c>
+      <c r="F74" s="23">
+        <v>19</v>
+      </c>
+      <c r="G74" s="23">
+        <v>52.6</v>
+      </c>
+      <c r="H74" s="23">
+        <v>2.23</v>
+      </c>
+      <c r="I74" s="23">
+        <v>1.66</v>
+      </c>
+      <c r="J74" s="19">
+        <v>122</v>
+      </c>
+      <c r="L74" s="12"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1932</v>
+      </c>
+      <c r="B75" s="5">
+        <v>12459</v>
+      </c>
+      <c r="C75" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="D75" s="23">
+        <v>29</v>
+      </c>
+      <c r="E75" s="23">
+        <v>13</v>
+      </c>
+      <c r="F75" s="23">
+        <v>16</v>
+      </c>
+      <c r="G75" s="23">
+        <v>54.3</v>
+      </c>
+      <c r="H75" s="23">
+        <v>1.95</v>
+      </c>
+      <c r="I75" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="J75" s="19">
+        <v>112</v>
+      </c>
+      <c r="L75" s="12"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1937</v>
+      </c>
+      <c r="B76" s="5">
+        <v>13545</v>
+      </c>
+      <c r="C76" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D76" s="23">
+        <v>26</v>
+      </c>
+      <c r="E76" s="23">
+        <v>13</v>
+      </c>
+      <c r="F76" s="23">
+        <v>13</v>
+      </c>
+      <c r="G76" s="23">
+        <v>54.3</v>
+      </c>
+      <c r="H76" s="23">
+        <v>1.75</v>
+      </c>
+      <c r="I76" s="23">
+        <v>1.34</v>
+      </c>
+      <c r="J76" s="19">
+        <v>112</v>
+      </c>
+      <c r="L76" s="12"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1942</v>
+      </c>
+      <c r="B77" s="5">
+        <v>14660</v>
+      </c>
+      <c r="C77" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D77" s="23">
+        <v>26</v>
+      </c>
+      <c r="E77" s="23">
+        <v>11</v>
+      </c>
+      <c r="F77" s="23">
+        <v>15</v>
+      </c>
+      <c r="G77" s="23">
+        <v>59.1</v>
+      </c>
+      <c r="H77" s="23">
+        <v>1.72</v>
+      </c>
+      <c r="I77" s="23">
+        <v>1.41</v>
+      </c>
+      <c r="J77" s="19">
+        <v>850</v>
+      </c>
+      <c r="L77" s="12"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1947</v>
+      </c>
+      <c r="B78" s="5">
+        <v>16069</v>
+      </c>
+      <c r="C78" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="D78" s="23">
+        <v>26</v>
+      </c>
+      <c r="E78" s="23">
+        <v>10</v>
+      </c>
+      <c r="F78" s="23">
+        <v>16</v>
+      </c>
+      <c r="G78" s="23">
+        <v>62</v>
+      </c>
+      <c r="H78" s="23">
+        <v>1.68</v>
+      </c>
+      <c r="I78" s="23">
+        <v>1.44</v>
+      </c>
+      <c r="J78" s="19">
+        <v>70</v>
+      </c>
+      <c r="L78" s="12"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B79" s="5"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="19"/>
+      <c r="L79" s="12"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="23"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="23"/>
+      <c r="G80" s="23"/>
+      <c r="H80" s="23"/>
+      <c r="I80" s="23"/>
+      <c r="J80" s="19"/>
+      <c r="L80" s="12"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="10"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="23"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="23"/>
+      <c r="G81" s="23"/>
+      <c r="H81" s="23"/>
+      <c r="I81" s="23"/>
+      <c r="J81" s="19"/>
+      <c r="L81" s="12"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D82" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F82" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H82" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I82" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J82" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L82" s="12"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1852</v>
+      </c>
+      <c r="B83" s="5">
+        <v>1536</v>
+      </c>
+      <c r="C83" s="3">
+        <v>0</v>
+      </c>
+      <c r="D83" s="23">
+        <v>44.6</v>
+      </c>
+      <c r="E83" s="23">
+        <v>35</v>
+      </c>
+      <c r="F83" s="23">
+        <v>9.6</v>
+      </c>
+      <c r="G83" s="23">
+        <v>29.1</v>
+      </c>
+      <c r="H83" s="23">
+        <v>3.09</v>
+      </c>
+      <c r="I83" s="23">
+        <v>1.29</v>
+      </c>
+      <c r="J83" s="19">
+        <v>331</v>
+      </c>
+      <c r="L83" s="12"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1857</v>
+      </c>
+      <c r="B84" s="5">
+        <v>1624</v>
+      </c>
+      <c r="C84" s="3">
+        <v>0</v>
+      </c>
+      <c r="D84" s="23">
+        <v>47.5</v>
+      </c>
+      <c r="E84" s="23">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="F84" s="23">
+        <v>12.8</v>
+      </c>
+      <c r="G84" s="23">
+        <v>29.9</v>
+      </c>
+      <c r="H84" s="23">
+        <v>3.28</v>
+      </c>
+      <c r="I84" s="23">
+        <v>1.41</v>
+      </c>
+      <c r="J84" s="19">
+        <v>322</v>
+      </c>
+      <c r="L84" s="12"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1862</v>
+      </c>
+      <c r="B85" s="5">
+        <v>1731</v>
+      </c>
+      <c r="C85" s="3">
+        <v>0</v>
+      </c>
+      <c r="D85" s="23">
+        <v>46.9</v>
+      </c>
+      <c r="E85" s="23">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="F85" s="23">
+        <v>12.6</v>
+      </c>
+      <c r="G85" s="23">
+        <v>30.2</v>
+      </c>
+      <c r="H85" s="23">
+        <v>3.25</v>
+      </c>
+      <c r="I85" s="23">
+        <v>1.41</v>
+      </c>
+      <c r="J85" s="19">
+        <v>319</v>
+      </c>
+      <c r="L85" s="12"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1867</v>
+      </c>
+      <c r="B86" s="5">
+        <v>1839</v>
+      </c>
+      <c r="C86" s="3">
+        <v>0</v>
+      </c>
+      <c r="D86" s="23">
+        <v>46.2</v>
+      </c>
+      <c r="E86" s="23">
+        <v>34.5</v>
+      </c>
+      <c r="F86" s="23">
+        <v>11.7</v>
+      </c>
+      <c r="G86" s="23">
+        <v>29.8</v>
+      </c>
+      <c r="H86" s="23">
+        <v>3.21</v>
+      </c>
+      <c r="I86" s="23">
+        <v>1.38</v>
+      </c>
+      <c r="J86" s="19">
+        <v>322</v>
+      </c>
+      <c r="L86" s="12"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1872</v>
+      </c>
+      <c r="B87" s="5">
+        <v>1959</v>
+      </c>
+      <c r="C87" s="3">
+        <v>0</v>
+      </c>
+      <c r="D87" s="23">
+        <v>47.5</v>
+      </c>
+      <c r="E87" s="23">
+        <v>34</v>
+      </c>
+      <c r="F87" s="23">
+        <v>13.5</v>
+      </c>
+      <c r="G87" s="23">
+        <v>30.5</v>
+      </c>
+      <c r="H87" s="23">
+        <v>3.31</v>
+      </c>
+      <c r="I87" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="J87" s="19">
+        <v>315</v>
+      </c>
+      <c r="L87" s="12"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1877</v>
+      </c>
+      <c r="B88" s="5">
+        <v>2083</v>
+      </c>
+      <c r="C88" s="3">
+        <v>0</v>
+      </c>
+      <c r="D88" s="23">
+        <v>44.9</v>
+      </c>
+      <c r="E88" s="23">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="F88" s="23">
+        <v>11.2</v>
+      </c>
+      <c r="G88" s="23">
+        <v>30.2</v>
+      </c>
+      <c r="H88" s="23">
+        <v>3.14</v>
+      </c>
+      <c r="I88" s="23">
+        <v>1.36</v>
+      </c>
+      <c r="J88" s="19">
+        <v>319</v>
+      </c>
+      <c r="L88" s="12"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1882</v>
+      </c>
+      <c r="B89" s="5">
+        <v>2219</v>
+      </c>
+      <c r="C89" s="3">
+        <v>0</v>
+      </c>
+      <c r="D89" s="23">
+        <v>48</v>
+      </c>
+      <c r="E89" s="23">
+        <v>33.9</v>
+      </c>
+      <c r="F89" s="23">
+        <v>14.1</v>
+      </c>
+      <c r="G89" s="23">
+        <v>30.7</v>
+      </c>
+      <c r="H89" s="23">
+        <v>3.36</v>
+      </c>
+      <c r="I89" s="23">
+        <v>1.48</v>
+      </c>
+      <c r="J89" s="19">
+        <v>314</v>
+      </c>
+      <c r="L89" s="12"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1887</v>
+      </c>
+      <c r="B90" s="5">
+        <v>2377</v>
+      </c>
+      <c r="C90" s="3">
+        <v>0</v>
+      </c>
+      <c r="D90" s="23">
+        <v>46.6</v>
+      </c>
+      <c r="E90" s="23">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F90" s="23">
+        <v>13.3</v>
+      </c>
+      <c r="G90" s="23">
+        <v>31</v>
+      </c>
+      <c r="H90" s="23">
+        <v>3.26</v>
+      </c>
+      <c r="I90" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="J90" s="19">
+        <v>310</v>
+      </c>
+      <c r="L90" s="12"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1892</v>
+      </c>
+      <c r="B91" s="5">
+        <v>2539</v>
+      </c>
+      <c r="C91" s="3">
+        <v>0</v>
+      </c>
+      <c r="D91" s="23">
+        <v>45.9</v>
+      </c>
+      <c r="E91" s="23">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="F91" s="23">
+        <v>13.2</v>
+      </c>
+      <c r="G91" s="23">
+        <v>31.3</v>
+      </c>
+      <c r="H91" s="23">
+        <v>3.21</v>
+      </c>
+      <c r="I91" s="23">
+        <v>1.44</v>
+      </c>
+      <c r="J91" s="19">
+        <v>307</v>
+      </c>
+      <c r="L91" s="12"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1897</v>
+      </c>
+      <c r="B92" s="5">
+        <v>2723</v>
+      </c>
+      <c r="C92" s="3">
+        <v>0</v>
+      </c>
+      <c r="D92" s="23">
+        <v>45</v>
+      </c>
+      <c r="E92" s="23">
+        <v>30.3</v>
+      </c>
+      <c r="F92" s="23">
+        <v>14.7</v>
+      </c>
+      <c r="G92" s="23">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="H92" s="23">
+        <v>3.15</v>
+      </c>
+      <c r="I92" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="J92" s="19">
+        <v>288</v>
+      </c>
+      <c r="L92" s="12"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1902</v>
+      </c>
+      <c r="B93" s="5">
+        <v>2919</v>
+      </c>
+      <c r="C93" s="3">
+        <v>0</v>
+      </c>
+      <c r="D93" s="23">
+        <v>44.7</v>
+      </c>
+      <c r="E93" s="23">
+        <v>31.6</v>
+      </c>
+      <c r="F93" s="23">
+        <v>13.1</v>
+      </c>
+      <c r="G93" s="23">
+        <v>32</v>
+      </c>
+      <c r="H93" s="23">
+        <v>3.12</v>
+      </c>
+      <c r="I93" s="23">
+        <v>1.44</v>
+      </c>
+      <c r="J93" s="19">
+        <v>300</v>
+      </c>
+      <c r="L93" s="12"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1907</v>
+      </c>
+      <c r="B94" s="5">
+        <v>3103</v>
+      </c>
+      <c r="C94" s="3">
+        <v>0</v>
+      </c>
+      <c r="D94" s="23">
+        <v>44.6</v>
+      </c>
+      <c r="E94" s="23">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="F94" s="23">
+        <v>11.4</v>
+      </c>
+      <c r="G94" s="23">
+        <v>30.5</v>
+      </c>
+      <c r="H94" s="23">
+        <v>3.09</v>
+      </c>
+      <c r="I94" s="23">
+        <v>1.36</v>
+      </c>
+      <c r="J94" s="19">
+        <v>316</v>
+      </c>
+      <c r="L94" s="12"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1912</v>
+      </c>
+      <c r="B95" s="5">
+        <v>3297</v>
+      </c>
+      <c r="C95" s="3">
+        <v>0</v>
+      </c>
+      <c r="D95" s="23">
+        <v>44.4</v>
+      </c>
+      <c r="E95" s="23">
+        <v>31.5</v>
+      </c>
+      <c r="F95" s="23">
+        <v>12.9</v>
+      </c>
+      <c r="G95" s="23">
+        <v>31.9</v>
+      </c>
+      <c r="H95" s="23">
+        <v>3.05</v>
+      </c>
+      <c r="I95" s="23">
+        <v>1.4</v>
+      </c>
+      <c r="J95" s="19">
+        <v>301</v>
+      </c>
+      <c r="L95" s="12"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1917</v>
+      </c>
+      <c r="B96" s="5">
+        <v>3511</v>
+      </c>
+      <c r="C96" s="3">
+        <v>0</v>
+      </c>
+      <c r="D96" s="23">
+        <v>43.3</v>
+      </c>
+      <c r="E96" s="23">
+        <v>31</v>
+      </c>
+      <c r="F96" s="23">
+        <v>12.3</v>
+      </c>
+      <c r="G96" s="23">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="H96" s="23">
+        <v>2.95</v>
+      </c>
+      <c r="I96" s="23">
+        <v>1.37</v>
+      </c>
+      <c r="J96" s="19">
+        <v>299</v>
+      </c>
+      <c r="L96" s="12"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1922</v>
+      </c>
+      <c r="B97" s="5">
+        <v>3721</v>
+      </c>
+      <c r="C97" s="3">
+        <v>0</v>
+      </c>
+      <c r="D97" s="23">
+        <v>42.2</v>
+      </c>
+      <c r="E97" s="23">
+        <v>31.3</v>
+      </c>
+      <c r="F97" s="23">
+        <v>10.9</v>
+      </c>
+      <c r="G97" s="23">
+        <v>31.6</v>
+      </c>
+      <c r="H97" s="23">
+        <v>2.86</v>
+      </c>
+      <c r="I97" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="J97" s="19">
+        <v>304</v>
+      </c>
+      <c r="L97" s="12"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1927</v>
+      </c>
+      <c r="B98" s="5">
+        <v>3994</v>
+      </c>
+      <c r="C98" s="3">
+        <v>0</v>
+      </c>
+      <c r="D98" s="23">
+        <v>43.8</v>
+      </c>
+      <c r="E98" s="23">
+        <v>26.4</v>
+      </c>
+      <c r="F98" s="23">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G98" s="23">
+        <v>37</v>
+      </c>
+      <c r="H98" s="23">
+        <v>2.99</v>
+      </c>
+      <c r="I98" s="23">
+        <v>1.58</v>
+      </c>
+      <c r="J98" s="19">
+        <v>254</v>
+      </c>
+      <c r="L98" s="12"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1932</v>
+      </c>
+      <c r="B99" s="5">
+        <v>4338</v>
+      </c>
+      <c r="C99" s="3">
+        <v>0</v>
+      </c>
+      <c r="D99" s="23">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="E99" s="23">
+        <v>24.5</v>
+      </c>
+      <c r="F99" s="23">
+        <v>15.7</v>
+      </c>
+      <c r="G99" s="23">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="H99" s="23">
+        <v>2.78</v>
+      </c>
+      <c r="I99" s="23">
+        <v>1.54</v>
+      </c>
+      <c r="J99" s="19">
+        <v>240</v>
+      </c>
+      <c r="L99" s="12"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1937</v>
+      </c>
+      <c r="B100" s="5">
+        <v>4679</v>
+      </c>
+      <c r="C100" s="3">
+        <v>0</v>
+      </c>
+      <c r="D100" s="23">
+        <v>38.4</v>
+      </c>
+      <c r="E100" s="23">
+        <v>23.8</v>
+      </c>
+      <c r="F100" s="23">
+        <v>14.6</v>
+      </c>
+      <c r="G100" s="23">
+        <v>39.1</v>
+      </c>
+      <c r="H100" s="23">
+        <v>2.68</v>
+      </c>
+      <c r="I100" s="23">
+        <v>1.49</v>
+      </c>
+      <c r="J100" s="19">
+        <v>237</v>
+      </c>
+      <c r="L100" s="12"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1942</v>
+      </c>
+      <c r="B101" s="5">
+        <v>5078</v>
+      </c>
+      <c r="C101" s="3">
+        <v>0</v>
+      </c>
+      <c r="D101" s="23">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="E101" s="23">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F101" s="23">
+        <v>18.2</v>
+      </c>
+      <c r="G101" s="23">
+        <v>44</v>
+      </c>
+      <c r="H101" s="23">
+        <v>2.69</v>
+      </c>
+      <c r="I101" s="23">
+        <v>1.68</v>
+      </c>
+      <c r="J101" s="19">
+        <v>200</v>
+      </c>
+      <c r="L101" s="12"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1947</v>
+      </c>
+      <c r="B102" s="5">
+        <v>5579</v>
+      </c>
+      <c r="C102" s="3">
+        <v>0</v>
+      </c>
+      <c r="D102" s="23">
+        <v>37</v>
+      </c>
+      <c r="E102" s="23">
+        <v>17.5</v>
+      </c>
+      <c r="F102" s="23">
+        <v>19.5</v>
+      </c>
+      <c r="G102" s="23">
+        <v>47.9</v>
+      </c>
+      <c r="H102" s="23">
+        <v>2.62</v>
+      </c>
+      <c r="I102" s="23">
+        <v>1.76</v>
+      </c>
+      <c r="J102" s="19">
+        <v>173</v>
+      </c>
+      <c r="L102" s="12"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>1952</v>
+      </c>
+      <c r="B103" s="5">
+        <v>6208</v>
+      </c>
+      <c r="C103" s="3">
+        <v>0</v>
+      </c>
+      <c r="D103" s="23">
+        <v>36.9</v>
+      </c>
+      <c r="E103" s="23">
+        <v>13.7</v>
+      </c>
+      <c r="F103" s="23">
+        <v>23.3</v>
+      </c>
+      <c r="G103" s="23">
+        <v>54.5</v>
+      </c>
+      <c r="H103" s="23">
+        <v>2.62</v>
+      </c>
+      <c r="I103" s="23">
+        <v>1.97</v>
+      </c>
+      <c r="J103" s="19">
+        <v>132</v>
+      </c>
+      <c r="L103" s="12"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>1957</v>
+      </c>
+      <c r="B104" s="5">
+        <v>7005</v>
+      </c>
+      <c r="C104" s="3">
+        <v>0</v>
+      </c>
+      <c r="D104" s="23">
+        <v>37.5</v>
+      </c>
+      <c r="E104" s="23">
+        <v>12.5</v>
+      </c>
+      <c r="F104" s="23">
+        <v>25.1</v>
+      </c>
+      <c r="G104" s="23">
+        <v>57.3</v>
+      </c>
+      <c r="H104" s="23">
+        <v>2.71</v>
+      </c>
+      <c r="I104" s="23">
+        <v>2.12</v>
+      </c>
+      <c r="J104" s="19">
+        <v>117</v>
+      </c>
+      <c r="L104" s="12"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>1962</v>
+      </c>
+      <c r="B105" s="5">
+        <v>7915</v>
+      </c>
+      <c r="C105" s="3">
+        <v>0</v>
+      </c>
+      <c r="D105" s="23">
+        <v>35.6</v>
+      </c>
+      <c r="E105" s="23">
+        <v>11.8</v>
+      </c>
+      <c r="F105" s="23">
+        <v>23.8</v>
+      </c>
+      <c r="G105" s="23">
+        <v>58.6</v>
+      </c>
+      <c r="H105" s="23">
+        <v>2.62</v>
+      </c>
+      <c r="I105" s="23">
+        <v>2.09</v>
+      </c>
+      <c r="J105" s="19">
+        <v>110</v>
+      </c>
+      <c r="L105" s="12"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B106" s="5"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="23"/>
+      <c r="E106" s="23"/>
+      <c r="F106" s="23"/>
+      <c r="G106" s="23"/>
+      <c r="H106" s="23"/>
+      <c r="I106" s="23"/>
+      <c r="J106" s="19"/>
+      <c r="L106" s="12"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B107" s="5"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="23"/>
+      <c r="E107" s="23"/>
+      <c r="F107" s="23"/>
+      <c r="G107" s="23"/>
+      <c r="H107" s="23"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="19"/>
+      <c r="L107" s="12"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="10"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="23"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+      <c r="G108" s="23"/>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="19"/>
+      <c r="L108" s="12"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C109" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D109" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E109" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F109" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G109" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H109" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I109" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J109" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L109" s="12"/>
+      <c r="O109" s="21"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1897</v>
+      </c>
+      <c r="B110" s="5">
+        <v>12969</v>
+      </c>
+      <c r="C110" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="D110" s="23">
+        <v>46.9</v>
+      </c>
+      <c r="E110" s="23">
+        <v>34.1</v>
+      </c>
+      <c r="F110" s="23">
+        <v>12.8</v>
+      </c>
+      <c r="G110" s="23">
+        <v>29.2</v>
+      </c>
+      <c r="H110" s="23">
+        <v>3.03</v>
+      </c>
+      <c r="I110" s="23">
+        <v>1.34</v>
+      </c>
+      <c r="J110" s="19">
+        <v>308</v>
+      </c>
+      <c r="L110" s="12"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1902</v>
+      </c>
+      <c r="B111" s="5">
+        <v>13803</v>
+      </c>
+      <c r="C111" s="3">
+        <v>-0.6</v>
+      </c>
+      <c r="D111" s="23">
+        <v>46.1</v>
+      </c>
+      <c r="E111" s="23">
+        <v>33.1</v>
+      </c>
+      <c r="F111" s="23">
+        <v>13</v>
+      </c>
+      <c r="G111" s="23">
+        <v>29.8</v>
+      </c>
+      <c r="H111" s="23">
+        <v>2.94</v>
+      </c>
+      <c r="I111" s="23">
+        <v>1.33</v>
+      </c>
+      <c r="J111" s="19">
+        <v>300</v>
+      </c>
+      <c r="L111" s="12"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>1907</v>
+      </c>
+      <c r="B112" s="5">
+        <v>14679</v>
+      </c>
+      <c r="C112" s="3">
+        <v>-0.6</v>
+      </c>
+      <c r="D112" s="23">
+        <v>45.6</v>
+      </c>
+      <c r="E112" s="23">
+        <v>32.6</v>
+      </c>
+      <c r="F112" s="23">
+        <v>13</v>
+      </c>
+      <c r="G112" s="23">
+        <v>30.3</v>
+      </c>
+      <c r="H112" s="23">
+        <v>2.88</v>
+      </c>
+      <c r="I112" s="23">
+        <v>1.32</v>
+      </c>
+      <c r="J112" s="19">
+        <v>296</v>
+      </c>
+      <c r="L112" s="12"/>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>1912</v>
+      </c>
+      <c r="B113" s="5">
+        <v>14936</v>
+      </c>
+      <c r="C113" s="3">
+        <v>-1.9</v>
+      </c>
+      <c r="D113" s="23">
+        <v>42.8</v>
+      </c>
+      <c r="E113" s="23">
+        <v>46.2</v>
+      </c>
+      <c r="F113" s="23">
+        <v>-3.3</v>
+      </c>
+      <c r="G113" s="23">
+        <v>20</v>
+      </c>
+      <c r="H113" s="23">
+        <v>2.64</v>
+      </c>
+      <c r="I113" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="J113" s="19">
+        <v>423</v>
+      </c>
+      <c r="L113" s="12"/>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>1917</v>
+      </c>
+      <c r="B114" s="5">
+        <v>14435</v>
+      </c>
+      <c r="C114" s="3">
+        <v>-0.6</v>
+      </c>
+      <c r="D114" s="23">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="E114" s="23">
+        <v>47.8</v>
+      </c>
+      <c r="F114" s="23">
+        <v>-7.6</v>
+      </c>
+      <c r="G114" s="23">
+        <v>17.8</v>
+      </c>
+      <c r="H114" s="23">
+        <v>2.36</v>
+      </c>
+      <c r="I114" s="23">
+        <v>0.63</v>
+      </c>
+      <c r="J114" s="24">
+        <v>456</v>
+      </c>
+      <c r="L114" s="12"/>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>1922</v>
+      </c>
+      <c r="B115" s="5">
+        <v>14708</v>
+      </c>
+      <c r="C115" s="3">
+        <v>-0.9</v>
+      </c>
+      <c r="D115" s="23">
+        <v>44.9</v>
+      </c>
+      <c r="E115" s="23">
+        <v>28.1</v>
+      </c>
+      <c r="F115" s="23">
+        <v>16.7</v>
+      </c>
+      <c r="G115" s="23">
+        <v>34</v>
+      </c>
+      <c r="H115" s="23">
+        <v>2.58</v>
+      </c>
+      <c r="I115" s="23">
+        <v>1.32</v>
+      </c>
+      <c r="J115" s="19">
+        <v>259</v>
+      </c>
+      <c r="L115" s="12"/>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>1927</v>
+      </c>
+      <c r="B116" s="5">
+        <v>15937</v>
+      </c>
+      <c r="C116" s="3">
+        <v>-1</v>
+      </c>
+      <c r="D116" s="23">
+        <v>43.9</v>
+      </c>
+      <c r="E116" s="23">
+        <v>26.5</v>
+      </c>
+      <c r="F116" s="23">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G116" s="23">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="H116" s="23">
+        <v>2.64</v>
+      </c>
+      <c r="I116" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="J116" s="19">
+        <v>234</v>
+      </c>
+      <c r="L116" s="12"/>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>1932</v>
+      </c>
+      <c r="B117" s="5">
+        <v>17358</v>
+      </c>
+      <c r="C117" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="D117" s="23">
+        <v>43.8</v>
+      </c>
+      <c r="E117" s="23">
+        <v>26.5</v>
+      </c>
+      <c r="F117" s="23">
+        <v>17.2</v>
+      </c>
+      <c r="G117" s="23">
+        <v>37</v>
+      </c>
+      <c r="H117" s="23">
+        <v>2.85</v>
+      </c>
+      <c r="I117" s="23">
+        <v>1.58</v>
+      </c>
+      <c r="J117" s="19">
+        <v>233</v>
+      </c>
+      <c r="L117" s="12"/>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>1937</v>
+      </c>
+      <c r="B118" s="5">
+        <v>19101</v>
+      </c>
+      <c r="C118" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="D118" s="23">
+        <v>43.2</v>
+      </c>
+      <c r="E118" s="23">
+        <v>23.3</v>
+      </c>
+      <c r="F118" s="23">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G118" s="23">
+        <v>40.6</v>
+      </c>
+      <c r="H118" s="23">
+        <v>3.09</v>
+      </c>
+      <c r="I118" s="23">
+        <v>1.86</v>
+      </c>
+      <c r="J118" s="19">
+        <v>203</v>
+      </c>
+      <c r="L118" s="12"/>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>1942</v>
+      </c>
+      <c r="B119" s="5">
+        <v>21208</v>
+      </c>
+      <c r="C119" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="D119" s="23">
+        <v>43.5</v>
+      </c>
+      <c r="E119" s="23">
+        <v>21.7</v>
+      </c>
+      <c r="F119" s="23">
+        <v>21.8</v>
+      </c>
+      <c r="G119" s="23">
+        <v>42.9</v>
+      </c>
+      <c r="H119" s="23">
+        <v>3.29</v>
+      </c>
+      <c r="I119" s="23">
+        <v>2.08</v>
+      </c>
+      <c r="J119" s="19">
+        <v>186</v>
+      </c>
+      <c r="L119" s="12"/>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>1947</v>
+      </c>
+      <c r="B120" s="5">
+        <v>23889</v>
+      </c>
+      <c r="C120" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="D120" s="23">
+        <v>44.3</v>
+      </c>
+      <c r="E120" s="23">
+        <v>17.7</v>
+      </c>
+      <c r="F120" s="23">
+        <v>26.5</v>
+      </c>
+      <c r="G120" s="23">
+        <v>48.4</v>
+      </c>
+      <c r="H120" s="23">
+        <v>3.36</v>
+      </c>
+      <c r="I120" s="23">
+        <v>2.36</v>
+      </c>
+      <c r="J120" s="19">
+        <v>148</v>
+      </c>
+      <c r="L120" s="12"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>1952</v>
+      </c>
+      <c r="B121" s="5">
+        <v>27567</v>
+      </c>
+      <c r="C121" s="3">
+        <v>-1.5</v>
+      </c>
+      <c r="D121" s="23">
+        <v>50</v>
+      </c>
+      <c r="E121" s="23">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F121" s="23">
+        <v>32.6</v>
+      </c>
+      <c r="G121" s="23">
+        <v>50</v>
+      </c>
+      <c r="H121" s="23">
+        <v>3.78</v>
+      </c>
+      <c r="I121" s="23">
+        <v>2.73</v>
+      </c>
+      <c r="J121" s="19">
+        <v>137</v>
+      </c>
+      <c r="L121" s="12"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>1957</v>
+      </c>
+      <c r="B122" s="5">
+        <v>32388</v>
+      </c>
+      <c r="C122" s="3">
+        <v>-1.2</v>
+      </c>
+      <c r="D122" s="23">
+        <v>48.6</v>
+      </c>
+      <c r="E122" s="23">
+        <v>14</v>
+      </c>
+      <c r="F122" s="23">
+        <v>34.6</v>
+      </c>
+      <c r="G122" s="23">
+        <v>54.9</v>
+      </c>
+      <c r="H122" s="23">
+        <v>3.73</v>
+      </c>
+      <c r="I122" s="23">
+        <v>2.91</v>
+      </c>
+      <c r="J122" s="19">
+        <v>108</v>
+      </c>
+      <c r="L122" s="12"/>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>1962</v>
+      </c>
+      <c r="B123" s="5">
+        <v>38284</v>
+      </c>
+      <c r="C123" s="3">
+        <v>-1.9</v>
+      </c>
+      <c r="D123" s="23">
+        <v>47.3</v>
+      </c>
+      <c r="E123" s="23">
+        <v>11.9</v>
+      </c>
+      <c r="F123" s="23">
+        <v>35.4</v>
+      </c>
+      <c r="G123" s="23">
+        <v>58</v>
+      </c>
+      <c r="H123" s="23">
+        <v>3.69</v>
+      </c>
+      <c r="I123" s="23">
+        <v>3.01</v>
+      </c>
+      <c r="J123" s="19">
+        <v>91</v>
+      </c>
+      <c r="L123" s="12"/>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>1967</v>
+      </c>
+      <c r="B124" s="5">
+        <v>45312</v>
+      </c>
+      <c r="C124" s="3">
+        <v>-1.6</v>
+      </c>
+      <c r="D124" s="23">
+        <v>46.1</v>
+      </c>
+      <c r="E124" s="23">
+        <v>10.7</v>
+      </c>
+      <c r="F124" s="23">
+        <v>35.4</v>
+      </c>
+      <c r="G124" s="23">
+        <v>59.5</v>
+      </c>
+      <c r="H124" s="23">
+        <v>3.62</v>
+      </c>
+      <c r="I124" s="23">
+        <v>3.02</v>
+      </c>
+      <c r="J124" s="19">
+        <v>83</v>
+      </c>
+      <c r="L124" s="12"/>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>1972</v>
+      </c>
+      <c r="B125" s="5">
+        <v>53621</v>
+      </c>
+      <c r="C125" s="3">
+        <v>-1.3</v>
+      </c>
+      <c r="D125" s="23">
+        <v>44.3</v>
+      </c>
+      <c r="E125" s="23">
+        <v>9.5</v>
+      </c>
+      <c r="F125" s="23">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="G125" s="23">
+        <v>61.1</v>
+      </c>
+      <c r="H125" s="23">
+        <v>3.36</v>
+      </c>
+      <c r="I125" s="23">
+        <v>2.87</v>
+      </c>
+      <c r="J125" s="19">
+        <v>75</v>
+      </c>
+      <c r="L125" s="12"/>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>1977</v>
+      </c>
+      <c r="B126" s="5">
+        <v>62752</v>
+      </c>
+      <c r="C126" s="3">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="D126" s="23">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E126" s="23">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F126" s="23">
+        <v>30.6</v>
+      </c>
+      <c r="G126" s="23">
+        <v>62.6</v>
+      </c>
+      <c r="H126" s="23">
+        <v>2.77</v>
+      </c>
+      <c r="I126" s="23">
+        <v>2.41</v>
+      </c>
+      <c r="J126" s="19">
+        <v>67</v>
+      </c>
+      <c r="L126" s="12"/>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B127" s="5"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="23"/>
+      <c r="E127" s="23"/>
+      <c r="F127" s="23"/>
+      <c r="G127" s="23"/>
+      <c r="H127" s="23"/>
+      <c r="I127" s="23"/>
+      <c r="J127" s="19"/>
+      <c r="L127" s="12"/>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B128" s="5"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="23"/>
+      <c r="E128" s="23"/>
+      <c r="F128" s="23"/>
+      <c r="G128" s="23"/>
+      <c r="H128" s="23"/>
+      <c r="I128" s="23"/>
+      <c r="J128" s="19"/>
+      <c r="L128" s="12"/>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B129" s="5"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="23"/>
+      <c r="E129" s="23"/>
+      <c r="F129" s="23"/>
+      <c r="G129" s="23"/>
+      <c r="H129" s="23"/>
+      <c r="I129" s="23"/>
+      <c r="J129" s="19"/>
+      <c r="L129" s="12"/>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B130" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C130" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D130" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E130" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F130" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G130" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H130" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I130" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J130" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L130" s="12"/>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>1902</v>
+      </c>
+      <c r="B131" s="5">
+        <v>1746</v>
+      </c>
+      <c r="C131" s="3">
+        <v>5</v>
+      </c>
+      <c r="D131" s="23">
+        <v>44.7</v>
+      </c>
+      <c r="E131" s="23">
+        <v>23.7</v>
+      </c>
+      <c r="F131" s="23">
+        <v>21</v>
+      </c>
+      <c r="G131" s="23">
+        <v>38.4</v>
+      </c>
+      <c r="H131" s="23">
+        <v>2.88</v>
+      </c>
+      <c r="I131" s="23">
+        <v>1.64</v>
+      </c>
+      <c r="J131" s="19">
+        <v>221</v>
+      </c>
+      <c r="L131" s="12"/>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>1907</v>
+      </c>
+      <c r="B132" s="5">
+        <v>2020</v>
+      </c>
+      <c r="C132" s="3">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D132" s="23">
+        <v>47.5</v>
+      </c>
+      <c r="E132" s="23">
+        <v>23.4</v>
+      </c>
+      <c r="F132" s="23">
+        <v>24.2</v>
+      </c>
+      <c r="G132" s="23">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="H132" s="23">
+        <v>2.95</v>
+      </c>
+      <c r="I132" s="23">
+        <v>1.73</v>
+      </c>
+      <c r="J132" s="19">
+        <v>214</v>
+      </c>
+      <c r="L132" s="12"/>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>1912</v>
+      </c>
+      <c r="B133" s="5">
+        <v>2363</v>
+      </c>
+      <c r="C133" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="D133" s="23">
+        <v>44.9</v>
+      </c>
+      <c r="E133" s="23">
+        <v>21.4</v>
+      </c>
+      <c r="F133" s="23">
+        <v>23.4</v>
+      </c>
+      <c r="G133" s="23">
+        <v>41.5</v>
+      </c>
+      <c r="H133" s="23">
+        <v>2.73</v>
+      </c>
+      <c r="I133" s="23">
+        <v>1.67</v>
+      </c>
+      <c r="J133" s="19">
+        <v>196</v>
+      </c>
+      <c r="L133" s="12"/>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>1917</v>
+      </c>
+      <c r="B134" s="5">
+        <v>2744</v>
+      </c>
+      <c r="C134" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="D134" s="23">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E134" s="23">
+        <v>22.3</v>
+      </c>
+      <c r="F134" s="23">
+        <v>18.5</v>
+      </c>
+      <c r="G134" s="23">
+        <v>39.6</v>
+      </c>
+      <c r="H134" s="23">
+        <v>2.46</v>
+      </c>
+      <c r="I134" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="J134" s="19">
+        <v>211</v>
+      </c>
+      <c r="L134" s="12"/>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>1922</v>
+      </c>
+      <c r="B135" s="5">
+        <v>3204</v>
+      </c>
+      <c r="C135" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="D135" s="23">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="E135" s="23">
+        <v>19.3</v>
+      </c>
+      <c r="F135" s="23">
+        <v>17.5</v>
+      </c>
+      <c r="G135" s="23">
+        <v>42.6</v>
+      </c>
+      <c r="H135" s="23">
+        <v>2.15</v>
+      </c>
+      <c r="I135" s="23">
+        <v>1.35</v>
+      </c>
+      <c r="J135" s="19">
+        <v>188</v>
+      </c>
+      <c r="L135" s="12"/>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>1927</v>
+      </c>
+      <c r="B136" s="5">
+        <v>3645</v>
+      </c>
+      <c r="C136" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="D136" s="23">
+        <v>32.9</v>
+      </c>
+      <c r="E136" s="23">
+        <v>15.2</v>
+      </c>
+      <c r="F136" s="23">
+        <v>17.7</v>
+      </c>
+      <c r="G136" s="23">
+        <v>48.3</v>
+      </c>
+      <c r="H136" s="23">
+        <v>1.92</v>
+      </c>
+      <c r="I136" s="23">
+        <v>1.34</v>
+      </c>
+      <c r="J136" s="19">
+        <v>149</v>
+      </c>
+      <c r="L136" s="12"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>1932</v>
+      </c>
+      <c r="B137" s="5">
+        <v>3957</v>
+      </c>
+      <c r="C137" s="3">
+        <v>-4.8</v>
+      </c>
+      <c r="D137" s="23">
+        <v>31.3</v>
+      </c>
+      <c r="E137" s="23">
+        <v>13.3</v>
+      </c>
+      <c r="F137" s="23">
+        <v>18</v>
+      </c>
+      <c r="G137" s="23">
+        <v>51.5</v>
+      </c>
+      <c r="H137" s="23">
+        <v>1.96</v>
+      </c>
+      <c r="I137" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="J137" s="19">
+        <v>128</v>
+      </c>
+      <c r="L137" s="12"/>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>1937</v>
+      </c>
+      <c r="B138" s="5">
+        <v>4264</v>
+      </c>
+      <c r="C138" s="3">
+        <v>-1.5</v>
+      </c>
+      <c r="D138" s="23">
+        <v>31</v>
+      </c>
+      <c r="E138" s="23">
+        <v>12.8</v>
+      </c>
+      <c r="F138" s="23">
+        <v>18.2</v>
+      </c>
+      <c r="G138" s="23">
+        <v>53.2</v>
+      </c>
+      <c r="H138" s="23">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I138" s="23">
+        <v>1.56</v>
+      </c>
+      <c r="J138" s="19">
+        <v>118</v>
+      </c>
+      <c r="L138" s="12"/>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>1942</v>
+      </c>
+      <c r="B139" s="5">
+        <v>4687</v>
+      </c>
+      <c r="C139" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D139" s="23">
+        <v>32</v>
+      </c>
+      <c r="E139" s="23">
+        <v>10.9</v>
+      </c>
+      <c r="F139" s="23">
+        <v>21.1</v>
+      </c>
+      <c r="G139" s="23">
+        <v>58</v>
+      </c>
+      <c r="H139" s="23">
+        <v>2.15</v>
+      </c>
+      <c r="I139" s="23">
+        <v>1.75</v>
+      </c>
+      <c r="J139" s="19">
+        <v>91</v>
+      </c>
+      <c r="L139" s="12"/>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>1947</v>
+      </c>
+      <c r="B140" s="5">
+        <v>5218</v>
+      </c>
+      <c r="C140" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D140" s="23">
+        <v>29.9</v>
+      </c>
+      <c r="E140" s="23">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F140" s="23">
+        <v>21.3</v>
+      </c>
+      <c r="G140" s="23">
+        <v>63.5</v>
+      </c>
+      <c r="H140" s="23">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="I140" s="23">
+        <v>1.79</v>
+      </c>
+      <c r="J140" s="19">
+        <v>62</v>
+      </c>
+      <c r="L140" s="12"/>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>1952</v>
+      </c>
+      <c r="B141" s="5">
+        <v>5822</v>
+      </c>
+      <c r="C141" s="3">
+        <v>0</v>
+      </c>
+      <c r="D141" s="23">
+        <v>29.6</v>
+      </c>
+      <c r="E141" s="23">
+        <v>7.4</v>
+      </c>
+      <c r="F141" s="23">
+        <v>22.2</v>
+      </c>
+      <c r="G141" s="23">
+        <v>67.5</v>
+      </c>
+      <c r="H141" s="23">
+        <v>2.04</v>
+      </c>
+      <c r="I141" s="23">
+        <v>1.89</v>
+      </c>
+      <c r="J141" s="19">
+        <v>43</v>
+      </c>
+      <c r="L141" s="12"/>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>1957</v>
+      </c>
+      <c r="B142" s="5">
+        <v>6460</v>
+      </c>
+      <c r="C142" s="3">
+        <v>-0.5</v>
+      </c>
+      <c r="D142" s="23">
+        <v>27.3</v>
+      </c>
+      <c r="E142" s="23">
+        <v>7.2</v>
+      </c>
+      <c r="F142" s="23">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="G142" s="23">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="H142" s="23">
+        <v>1.9</v>
+      </c>
+      <c r="I142" s="23">
+        <v>1.78</v>
+      </c>
+      <c r="J142" s="19">
+        <v>37</v>
+      </c>
+      <c r="L142" s="12"/>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>1962</v>
+      </c>
+      <c r="B143" s="5">
+        <v>7153</v>
+      </c>
+      <c r="C143" s="3">
+        <v>-5.8</v>
+      </c>
+      <c r="D143" s="23">
+        <v>34.1</v>
+      </c>
+      <c r="E143" s="23">
+        <v>7.3</v>
+      </c>
+      <c r="F143" s="23">
+        <v>26.8</v>
+      </c>
+      <c r="G143" s="23">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="H143" s="23">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="I143" s="23">
+        <v>2.31</v>
+      </c>
+      <c r="J143" s="19">
+        <v>32</v>
+      </c>
+      <c r="L143" s="12"/>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>1967</v>
+      </c>
+      <c r="B144" s="5">
+        <v>7917</v>
+      </c>
+      <c r="C144" s="3">
+        <v>-6.2</v>
+      </c>
+      <c r="D144" s="23">
+        <v>32.5</v>
+      </c>
+      <c r="E144" s="23">
+        <v>7.1</v>
+      </c>
+      <c r="F144" s="23">
+        <v>25.4</v>
+      </c>
+      <c r="G144" s="23">
+        <v>71</v>
+      </c>
+      <c r="H144" s="23">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="I144" s="23">
+        <v>2.33</v>
+      </c>
+      <c r="J144" s="19">
+        <v>28</v>
+      </c>
+      <c r="L144" s="12"/>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B145" s="5"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="23"/>
+      <c r="E145" s="23"/>
+      <c r="F145" s="23"/>
+      <c r="G145" s="23"/>
+      <c r="H145" s="23"/>
+      <c r="I145" s="23"/>
+      <c r="J145" s="19"/>
+      <c r="L145" s="12"/>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B146" s="5"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="23"/>
+      <c r="E146" s="23"/>
+      <c r="F146" s="23"/>
+      <c r="G146" s="23"/>
+      <c r="H146" s="23"/>
+      <c r="I146" s="23"/>
+      <c r="J146" s="19"/>
+      <c r="L146" s="12"/>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B147" s="5"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="23"/>
+      <c r="E147" s="23"/>
+      <c r="F147" s="23"/>
+      <c r="G147" s="23"/>
+      <c r="H147" s="23"/>
+      <c r="I147" s="23"/>
+      <c r="J147" s="19"/>
+      <c r="L147" s="12"/>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B148" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C148" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D148" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E148" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F148" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G148" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H148" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I148" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J148" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L148" s="12"/>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>1887</v>
+      </c>
+      <c r="B149" s="5">
+        <v>1648</v>
+      </c>
+      <c r="C149" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D149" s="23">
+        <v>44.4</v>
+      </c>
+      <c r="E149" s="23">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="F149" s="23">
+        <v>12.1</v>
+      </c>
+      <c r="G149" s="23">
+        <v>30.6</v>
+      </c>
+      <c r="H149" s="23">
+        <v>2.95</v>
+      </c>
+      <c r="I149" s="23">
+        <v>1.33</v>
+      </c>
+      <c r="J149" s="19">
+        <v>314</v>
+      </c>
+      <c r="L149" s="12"/>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>1892</v>
+      </c>
+      <c r="B150" s="5">
+        <v>1778</v>
+      </c>
+      <c r="C150" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D150" s="23">
+        <v>45.5</v>
+      </c>
+      <c r="E150" s="23">
+        <v>28.2</v>
+      </c>
+      <c r="F150" s="23">
+        <v>17.3</v>
+      </c>
+      <c r="G150" s="23">
+        <v>34.4</v>
+      </c>
+      <c r="H150" s="23">
+        <v>2.95</v>
+      </c>
+      <c r="I150" s="23">
+        <v>1.49</v>
+      </c>
+      <c r="J150" s="19">
+        <v>278</v>
+      </c>
+      <c r="L150" s="12"/>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>1897</v>
+      </c>
+      <c r="B151" s="5">
+        <v>1924</v>
+      </c>
+      <c r="C151" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D151" s="23">
+        <v>43.1</v>
+      </c>
+      <c r="E151" s="23">
+        <v>29.4</v>
+      </c>
+      <c r="F151" s="23">
+        <v>13.7</v>
+      </c>
+      <c r="G151" s="23">
+        <v>32.9</v>
+      </c>
+      <c r="H151" s="23">
+        <v>2.74</v>
+      </c>
+      <c r="I151" s="23">
+        <v>1.33</v>
+      </c>
+      <c r="J151" s="19">
+        <v>291</v>
+      </c>
+      <c r="L151" s="12"/>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>1902</v>
+      </c>
+      <c r="B152" s="5">
+        <v>2057</v>
+      </c>
+      <c r="C152" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D152" s="23">
+        <v>41.8</v>
+      </c>
+      <c r="E152" s="23">
+        <v>29.2</v>
+      </c>
+      <c r="F152" s="23">
+        <v>12.6</v>
+      </c>
+      <c r="G152" s="23">
+        <v>32.9</v>
+      </c>
+      <c r="H152" s="23">
+        <v>2.61</v>
+      </c>
+      <c r="I152" s="23">
+        <v>1.26</v>
+      </c>
+      <c r="J152" s="19">
+        <v>292</v>
+      </c>
+      <c r="L152" s="12"/>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>1907</v>
+      </c>
+      <c r="B153" s="5">
+        <v>2202</v>
+      </c>
+      <c r="C153" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D153" s="23">
+        <v>43.6</v>
+      </c>
+      <c r="E153" s="23">
+        <v>29.9</v>
+      </c>
+      <c r="F153" s="23">
+        <v>13.7</v>
+      </c>
+      <c r="G153" s="23">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="H153" s="23">
+        <v>2.71</v>
+      </c>
+      <c r="I153" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="J153" s="19">
+        <v>294</v>
+      </c>
+      <c r="L153" s="12"/>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>1912</v>
+      </c>
+      <c r="B154" s="5">
+        <v>2380</v>
+      </c>
+      <c r="C154" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="D154" s="23">
+        <v>44.5</v>
+      </c>
+      <c r="E154" s="23">
+        <v>28.3</v>
+      </c>
+      <c r="F154" s="23">
+        <v>16.2</v>
+      </c>
+      <c r="G154" s="23">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="H154" s="23">
+        <v>2.82</v>
+      </c>
+      <c r="I154" s="23">
+        <v>1.44</v>
+      </c>
+      <c r="J154" s="19">
+        <v>274</v>
+      </c>
+      <c r="L154" s="12"/>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>1917</v>
+      </c>
+      <c r="B155" s="5">
+        <v>2558</v>
+      </c>
+      <c r="C155" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D155" s="23">
+        <v>41.4</v>
+      </c>
+      <c r="E155" s="23">
+        <v>29.7</v>
+      </c>
+      <c r="F155" s="23">
+        <v>11.7</v>
+      </c>
+      <c r="G155" s="23">
+        <v>32.9</v>
+      </c>
+      <c r="H155" s="23">
+        <v>2.69</v>
+      </c>
+      <c r="I155" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="J155" s="19">
+        <v>292</v>
+      </c>
+      <c r="L155" s="12"/>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>1922</v>
+      </c>
+      <c r="B156" s="5">
+        <v>2739</v>
+      </c>
+      <c r="C156" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D156" s="23">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="E156" s="23">
+        <v>24.5</v>
+      </c>
+      <c r="F156" s="23">
+        <v>15.2</v>
+      </c>
+      <c r="G156" s="23">
+        <v>38</v>
+      </c>
+      <c r="H156" s="23">
+        <v>2.63</v>
+      </c>
+      <c r="I156" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="J156" s="19">
+        <v>246</v>
+      </c>
+      <c r="L156" s="12"/>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>1927</v>
+      </c>
+      <c r="B157" s="5">
+        <v>2987</v>
+      </c>
+      <c r="C157" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D157" s="23">
+        <v>41.5</v>
+      </c>
+      <c r="E157" s="23">
+        <v>23</v>
+      </c>
+      <c r="F157" s="23">
+        <v>18.5</v>
+      </c>
+      <c r="G157" s="23">
+        <v>40.6</v>
+      </c>
+      <c r="H157" s="23">
+        <v>2.79</v>
+      </c>
+      <c r="I157" s="23">
+        <v>1.64</v>
+      </c>
+      <c r="J157" s="19">
+        <v>225</v>
+      </c>
+      <c r="L157" s="12"/>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>1932</v>
+      </c>
+      <c r="B158" s="5">
+        <v>3278</v>
+      </c>
+      <c r="C158" s="3">
+        <v>0</v>
+      </c>
+      <c r="D158" s="23">
+        <v>38.9</v>
+      </c>
+      <c r="E158" s="23">
+        <v>21</v>
+      </c>
+      <c r="F158" s="23">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="G158" s="23">
+        <v>43.2</v>
+      </c>
+      <c r="H158" s="23">
+        <v>2.63</v>
+      </c>
+      <c r="I158" s="23">
+        <v>1.63</v>
+      </c>
+      <c r="J158" s="19">
+        <v>206</v>
+      </c>
+      <c r="L158" s="12"/>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>1937</v>
+      </c>
+      <c r="B159" s="5">
+        <v>3602</v>
+      </c>
+      <c r="C159" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D159" s="23">
+        <v>39.5</v>
+      </c>
+      <c r="E159" s="23">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F159" s="23">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="G159" s="23">
+        <v>44.2</v>
+      </c>
+      <c r="H159" s="23">
+        <v>2.7</v>
+      </c>
+      <c r="I159" s="23">
+        <v>1.71</v>
+      </c>
+      <c r="J159" s="19">
+        <v>198</v>
+      </c>
+      <c r="L159" s="12"/>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>1942</v>
+      </c>
+      <c r="B160" s="5">
+        <v>3999</v>
+      </c>
+      <c r="C160" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D160" s="23">
+        <v>41</v>
+      </c>
+      <c r="E160" s="23">
+        <v>19.3</v>
+      </c>
+      <c r="F160" s="23">
+        <v>21.7</v>
+      </c>
+      <c r="G160" s="23">
+        <v>46.5</v>
+      </c>
+      <c r="H160" s="23">
+        <v>2.82</v>
+      </c>
+      <c r="I160" s="23">
+        <v>1.87</v>
+      </c>
+      <c r="J160" s="19">
+        <v>183</v>
+      </c>
+      <c r="L160" s="12"/>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>1947</v>
+      </c>
+      <c r="B161" s="5">
+        <v>4565</v>
+      </c>
+      <c r="C161" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="D161" s="23">
+        <v>43.8</v>
+      </c>
+      <c r="E161" s="23">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F161" s="23">
+        <v>27.6</v>
+      </c>
+      <c r="G161" s="23">
+        <v>52.1</v>
+      </c>
+      <c r="H161" s="23">
+        <v>3.05</v>
+      </c>
+      <c r="I161" s="23">
+        <v>2.23</v>
+      </c>
+      <c r="J161" s="19">
+        <v>147</v>
+      </c>
+      <c r="L161" s="12"/>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>1952</v>
+      </c>
+      <c r="B162" s="5">
+        <v>5424</v>
+      </c>
+      <c r="C162" s="3">
+        <v>6.6</v>
+      </c>
+      <c r="D162" s="23">
+        <v>44.4</v>
+      </c>
+      <c r="E162" s="23">
+        <v>12.4</v>
+      </c>
+      <c r="F162" s="23">
+        <v>32</v>
+      </c>
+      <c r="G162" s="23">
+        <v>58.8</v>
+      </c>
+      <c r="H162" s="23">
+        <v>3.11</v>
+      </c>
+      <c r="I162" s="23">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="J162" s="19">
+        <v>109</v>
+      </c>
+      <c r="L162" s="12"/>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>1957</v>
+      </c>
+      <c r="B163" s="5">
+        <v>6568</v>
+      </c>
+      <c r="C163" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="D163" s="23">
+        <v>44.5</v>
+      </c>
+      <c r="E163" s="23">
+        <v>10.8</v>
+      </c>
+      <c r="F163" s="23">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="G163" s="23">
+        <v>61.7</v>
+      </c>
+      <c r="H163" s="23">
+        <v>3.18</v>
+      </c>
+      <c r="I163" s="23">
+        <v>2.66</v>
+      </c>
+      <c r="J163" s="19">
+        <v>94</v>
+      </c>
+      <c r="L163" s="12"/>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B164" s="5"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="23"/>
+      <c r="E164" s="23"/>
+      <c r="F164" s="23"/>
+      <c r="G164" s="23"/>
+      <c r="H164" s="23"/>
+      <c r="I164" s="23"/>
+      <c r="J164" s="19"/>
+      <c r="L164" s="12"/>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B165" s="5"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="23"/>
+      <c r="E165" s="23"/>
+      <c r="F165" s="23"/>
+      <c r="G165" s="23"/>
+      <c r="H165" s="23"/>
+      <c r="I165" s="23"/>
+      <c r="J165" s="19"/>
+      <c r="L165" s="12"/>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B166" s="5"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="23"/>
+      <c r="E166" s="23"/>
+      <c r="F166" s="23"/>
+      <c r="G166" s="23"/>
+      <c r="H166" s="23"/>
+      <c r="I166" s="23"/>
+      <c r="J166" s="19"/>
+      <c r="L166" s="12"/>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B167" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C167" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D167" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E167" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F167" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G167" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H167" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I167" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="J167" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L167" s="12"/>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>1897</v>
+      </c>
+      <c r="B168" s="5">
+        <v>877</v>
+      </c>
+      <c r="C168" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D168" s="23">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E168" s="23">
+        <v>14.8</v>
+      </c>
+      <c r="F168" s="23">
+        <v>24.1</v>
+      </c>
+      <c r="G168" s="23">
+        <v>49.6</v>
+      </c>
+      <c r="H168" s="23">
+        <v>2.71</v>
+      </c>
+      <c r="I168" s="23">
+        <v>1.92</v>
+      </c>
+      <c r="J168" s="19">
+        <v>139</v>
+      </c>
+      <c r="L168" s="12"/>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>1902</v>
+      </c>
+      <c r="B169" s="5">
+        <v>994</v>
+      </c>
+      <c r="C169" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="D169" s="23">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E169" s="23">
+        <v>13.7</v>
+      </c>
+      <c r="F169" s="23">
+        <v>25.2</v>
+      </c>
+      <c r="G169" s="23">
+        <v>51.6</v>
+      </c>
+      <c r="H169" s="23">
+        <v>2.69</v>
+      </c>
+      <c r="I169" s="23">
+        <v>1.97</v>
+      </c>
+      <c r="J169" s="19">
+        <v>126</v>
+      </c>
+      <c r="L169" s="12"/>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>1907</v>
+      </c>
+      <c r="B170" s="5">
+        <v>1131</v>
+      </c>
+      <c r="C170" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D170" s="23">
+        <v>37.6</v>
+      </c>
+      <c r="E170" s="23">
+        <v>14</v>
+      </c>
+      <c r="F170" s="23">
+        <v>23.6</v>
+      </c>
+      <c r="G170" s="23">
+        <v>51.4</v>
+      </c>
+      <c r="H170" s="23">
+        <v>2.57</v>
+      </c>
+      <c r="I170" s="23">
+        <v>1.88</v>
+      </c>
+      <c r="J170" s="19">
+        <v>127</v>
+      </c>
+      <c r="L170" s="12"/>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>1912</v>
+      </c>
+      <c r="B171" s="5">
+        <v>1281</v>
+      </c>
+      <c r="C171" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D171" s="23">
+        <v>36.5</v>
+      </c>
+      <c r="E171" s="23">
+        <v>13.5</v>
+      </c>
+      <c r="F171" s="23">
+        <v>23</v>
+      </c>
+      <c r="G171" s="23">
+        <v>52.3</v>
+      </c>
+      <c r="H171" s="23">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="I171" s="23">
+        <v>1.83</v>
+      </c>
+      <c r="J171" s="19">
+        <v>121</v>
+      </c>
+      <c r="L171" s="12"/>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>1917</v>
+      </c>
+      <c r="B172" s="5">
+        <v>1423</v>
+      </c>
+      <c r="C172" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D172" s="23">
+        <v>31.9</v>
+      </c>
+      <c r="E172" s="23">
+        <v>14.1</v>
+      </c>
+      <c r="F172" s="23">
+        <v>17.8</v>
+      </c>
+      <c r="G172" s="23">
+        <v>50.8</v>
+      </c>
+      <c r="H172" s="23">
+        <v>2.14</v>
+      </c>
+      <c r="I172" s="23">
+        <v>1.55</v>
+      </c>
+      <c r="J172" s="19">
+        <v>131</v>
+      </c>
+      <c r="L172" s="12"/>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>1922</v>
+      </c>
+      <c r="B173" s="5">
+        <v>1565</v>
+      </c>
+      <c r="C173" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="D173" s="23">
+        <v>30.1</v>
+      </c>
+      <c r="E173" s="23">
+        <v>12.6</v>
+      </c>
+      <c r="F173" s="23">
+        <v>17.5</v>
+      </c>
+      <c r="G173" s="23">
+        <v>53.3</v>
+      </c>
+      <c r="H173" s="23">
+        <v>1.99</v>
+      </c>
+      <c r="I173" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="J173" s="19">
+        <v>116</v>
+      </c>
+      <c r="L173" s="12"/>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>1927</v>
+      </c>
+      <c r="B174" s="5">
+        <v>1731</v>
+      </c>
+      <c r="C174" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="D174" s="23">
+        <v>28.6</v>
+      </c>
+      <c r="E174" s="23">
+        <v>11.9</v>
+      </c>
+      <c r="F174" s="23">
+        <v>16.7</v>
+      </c>
+      <c r="G174" s="23">
+        <v>54.9</v>
+      </c>
+      <c r="H174" s="23">
+        <v>1.82</v>
+      </c>
+      <c r="I174" s="23">
+        <v>1.41</v>
+      </c>
+      <c r="J174" s="19">
+        <v>106</v>
+      </c>
+      <c r="L174" s="12"/>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>1932</v>
+      </c>
+      <c r="B175" s="5">
+        <v>1893</v>
+      </c>
+      <c r="C175" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="D175" s="23">
+        <v>25.8</v>
+      </c>
+      <c r="E175" s="23">
+        <v>11.5</v>
+      </c>
+      <c r="F175" s="23">
+        <v>14.3</v>
+      </c>
+      <c r="G175" s="23">
+        <v>55.9</v>
+      </c>
+      <c r="H175" s="23">
+        <v>1.59</v>
+      </c>
+      <c r="I175" s="23">
+        <v>1.25</v>
+      </c>
+      <c r="J175" s="19">
+        <v>100</v>
+      </c>
+      <c r="L175" s="12"/>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>1937</v>
+      </c>
+      <c r="B176" s="5">
+        <v>2027</v>
+      </c>
+      <c r="C176" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="D176" s="23">
+        <v>22.3</v>
+      </c>
+      <c r="E176" s="23">
+        <v>11.1</v>
+      </c>
+      <c r="F176" s="23">
+        <v>11.2</v>
+      </c>
+      <c r="G176" s="23">
+        <v>56.8</v>
+      </c>
+      <c r="H176" s="23">
+        <v>1.37</v>
+      </c>
+      <c r="I176" s="23">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="J176" s="19">
+        <v>95</v>
+      </c>
+      <c r="L176" s="12"/>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>1942</v>
+      </c>
+      <c r="B177" s="5">
+        <v>2142</v>
+      </c>
+      <c r="C177" s="3">
+        <v>-0.8</v>
+      </c>
+      <c r="D177" s="23">
+        <v>21.6</v>
+      </c>
+      <c r="E177" s="23">
+        <v>10.3</v>
+      </c>
+      <c r="F177" s="23">
+        <v>11.3</v>
+      </c>
+      <c r="G177" s="23">
+        <v>59.5</v>
+      </c>
+      <c r="H177" s="23">
+        <v>1.33</v>
+      </c>
+      <c r="I177" s="23">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J177" s="19">
+        <v>81</v>
+      </c>
+      <c r="L177" s="12"/>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>1947</v>
+      </c>
+      <c r="B178" s="5">
+        <v>2269</v>
+      </c>
+      <c r="C178" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D178" s="23">
+        <v>21.1</v>
+      </c>
+      <c r="E178" s="23">
+        <v>9.1</v>
+      </c>
+      <c r="F178" s="23">
+        <v>12</v>
+      </c>
+      <c r="G178" s="23">
+        <v>63.6</v>
+      </c>
+      <c r="H178" s="23">
+        <v>1.32</v>
+      </c>
+      <c r="I178" s="23">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="J178" s="19">
+        <v>60</v>
+      </c>
+      <c r="L178" s="12"/>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>1952</v>
+      </c>
+      <c r="B179" s="5">
+        <v>2424</v>
+      </c>
+      <c r="C179" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="D179" s="23">
+        <v>21.2</v>
+      </c>
+      <c r="E179" s="23">
+        <v>8.5</v>
+      </c>
+      <c r="F179" s="23">
+        <v>12.7</v>
+      </c>
+      <c r="G179" s="23">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="H179" s="23">
+        <v>1.35</v>
+      </c>
+      <c r="I179" s="23">
+        <v>1.23</v>
+      </c>
+      <c r="J179" s="19">
+        <v>45</v>
+      </c>
+      <c r="L179" s="12"/>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>1957</v>
+      </c>
+      <c r="B180" s="5">
+        <v>2596</v>
+      </c>
+      <c r="C180" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D180" s="23">
+        <v>21.8</v>
+      </c>
+      <c r="E180" s="23">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F180" s="23">
+        <v>13</v>
+      </c>
+      <c r="G180" s="23">
+        <v>67.5</v>
+      </c>
+      <c r="H180" s="23">
+        <v>1.43</v>
+      </c>
+      <c r="I180" s="23">
+        <v>1.31</v>
+      </c>
+      <c r="J180" s="19">
+        <v>41</v>
+      </c>
+      <c r="L180" s="12"/>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>1962</v>
+      </c>
+      <c r="B181" s="5">
+        <v>2779</v>
+      </c>
+      <c r="C181" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D181" s="23">
+        <v>22</v>
+      </c>
+      <c r="E181" s="23">
+        <v>8.6</v>
+      </c>
+      <c r="F181" s="23">
+        <v>13.4</v>
+      </c>
+      <c r="G181" s="23">
+        <v>69.3</v>
+      </c>
+      <c r="H181" s="23">
+        <v>1.52</v>
+      </c>
+      <c r="I181" s="23">
+        <v>1.43</v>
+      </c>
+      <c r="J181" s="19">
+        <v>33</v>
+      </c>
+      <c r="L181" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
+++ b/rtss-mexico/src/main/resources/Latin-America-Vital-Rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D089DF-FD06-4D2C-BC92-C3CB2D0F9F11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF39C3C4-FE2C-4A08-955E-D31442B25531}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
+    <workbookView xWindow="19350" yWindow="690" windowWidth="16200" windowHeight="22275" activeTab="2" xr2:uid="{70974F82-9CB0-46B6-83A5-00B0CFE057A6}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="161">
   <si>
     <t>страна</t>
   </si>
@@ -521,6 +521,9 @@
   </si>
   <si>
     <t>брутто-коэффициент воспроизводства: среднее число дочерей на женщину при данной рождаемости, без учёта смертности женщин до и в репродуктивных возрастах</t>
+  </si>
+  <si>
+    <t>Доп. см. в файле Latin-America-Vital-Rates-Yearly.xlsx</t>
   </si>
 </sst>
 </file>
@@ -608,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -648,6 +651,12 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -963,172 +972,328 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C2E48C-64F2-4716-9126-743AC29B124D}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="26">
+        <v>1881</v>
+      </c>
+      <c r="D10" s="27">
+        <v>47</v>
+      </c>
+      <c r="E10" s="27">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="26">
+        <v>1890</v>
+      </c>
+      <c r="D11" s="27">
+        <v>46.5</v>
+      </c>
+      <c r="E11" s="27">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="26">
+        <v>1900</v>
+      </c>
+      <c r="D12" s="27">
+        <v>46</v>
+      </c>
+      <c r="E12" s="27">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="26">
+        <v>1910</v>
+      </c>
+      <c r="D13" s="27">
+        <v>45.5</v>
+      </c>
+      <c r="E13" s="27">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="26">
+        <v>1920</v>
+      </c>
+      <c r="D14" s="27">
+        <v>45</v>
+      </c>
+      <c r="E14" s="27">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="26">
+        <v>1930</v>
+      </c>
+      <c r="D15" s="27">
+        <v>44.8</v>
+      </c>
+      <c r="E15" s="27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="26">
+        <v>1945</v>
+      </c>
+      <c r="D16" s="27">
+        <v>44.4</v>
+      </c>
+      <c r="E16" s="27">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="26">
+        <v>1955</v>
+      </c>
+      <c r="D17" s="27">
+        <v>43.2</v>
+      </c>
+      <c r="E17" s="27">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="26">
+        <v>1965</v>
+      </c>
+      <c r="D18" s="27">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="E18" s="27">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="26">
+        <v>1975</v>
+      </c>
+      <c r="D19" s="27">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="E19" s="27">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="26">
+        <v>1985</v>
+      </c>
+      <c r="D20" s="27">
+        <v>28.99</v>
+      </c>
+      <c r="E20" s="27">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="26">
+        <v>1995</v>
+      </c>
+      <c r="D21" s="27">
+        <v>21.93</v>
+      </c>
+      <c r="E21" s="27">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="26">
+        <v>2000</v>
+      </c>
+      <c r="D22" s="27">
+        <v>21.13</v>
+      </c>
+      <c r="E22" s="27">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="26">
+        <v>2007</v>
+      </c>
+      <c r="D23" s="27">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="E23" s="27">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="3" t="s">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="3" t="s">
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="3" t="s">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="3" t="s">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9566,8 +9731,12 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="N12" s="6">
+        <v>20.5</v>
+      </c>
+      <c r="O12" s="6">
+        <v>19.100000000000001</v>
+      </c>
       <c r="P12" s="3">
         <v>25.14</v>
       </c>
